--- a/docs/page-copy/07-我们的成就.xlsx
+++ b/docs/page-copy/07-我们的成就.xlsx
@@ -397,16 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G139"/>
-  <cols>
-    <col min="1" max="1" width="36.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="72.83203125" customWidth="1"/>
-    <col min="5" max="5" width="72.83203125" customWidth="1"/>
-    <col min="6" max="6" width="48.83203125" customWidth="1"/>
-    <col min="7" max="7" width="28.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:G132"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,80 +422,78 @@
         <v>notes</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>achievementsReport.abstract.body</v>
+        <v>achievementsReport.callout.principalLabel</v>
       </c>
       <c r="B2" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C2" t="str">
-        <v>paragraph / other</v>
-      </c>
-      <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">This report synthesizes one documented year (**2025**) of **TikTok Live** sessions coordinated with **Master Spirits**: headline quantities, baseline observations on **American attached spirits (ghosts)**, routine mental-disorder–related presentations, structured session techniques, self-reported outcomes, exploratory procedures, and  highlighted special cases.
-It foregrounds **transparent field documentation**; it is **not** framed as a randomized controlled trial.</v>
-      </c>
-      <c r="E2" t="str" xml:space="preserve">
-        <v xml:space="preserve">本文档为**灰文献式汇总**：**2025** 年度在 **TikTok 直播**内、与 **master spirit** 协同的田野记录——**核心量级**、**美国附体鬼魂（ghosts）**基线、**mental disorder** 相关呈现、技术路径、自述转归、探索步骤与**四则**突出个案。
-侧重**过程透明**，**不**宣称等同**随机对照试验**。</v>
+        <v>heading</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Within 30 minutes</v>
+      </c>
+      <c r="E2" t="str">
+        <v>三十分钟内</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>achievementsReport.abstract.title</v>
+        <v>achievementsReport.carouselNote</v>
       </c>
       <c r="B3" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C3" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D3" t="str">
-        <v>Abstract</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v>摘要</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>achievementsReport.callout.principalLabel</v>
+        <v>achievementsReport.case.1</v>
       </c>
       <c r="B4" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C4" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D4" t="str">
-        <v>Principal observation</v>
+        <v>August 11 livestream: depression and bipolar disorder untreated &gt;15 years — eased within thirty minutes with no recurrence reported.</v>
       </c>
       <c r="E4" t="str">
-        <v>主要结论</v>
+        <v>八月十一日直播间：超过十五年未治愈的抑郁，双向---在三十分钟内缓解并且再无复发</v>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>achievementsReport.carouselNote</v>
+        <v>achievementsReport.case.2</v>
       </c>
       <c r="B5" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -513,21 +502,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D5" t="str">
-        <v>Placeholder gallery — replace slides in `carouselSlides` with captures from the YouTube replay channel.</v>
+        <v>June 14 livestream: long-standing PTSD — fully cleared in one spirit (ghost) regulation session; trauma residue dissipated.</v>
       </c>
       <c r="E5" t="str">
-        <v>示意多图相册（请将 `carouselSlides` 替换为 YouTube 直播回放频道截图）。</v>
+        <v>六月十四日直播间：困扰多年的PTSD---在一次鬼魂控制中就得到了完全疏通，心灵创伤消散</v>
       </c>
       <c r="F5" t="str">
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>achievementsReport.case.1</v>
+        <v>achievementsReport.case.3</v>
       </c>
       <c r="B6" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -536,21 +525,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D6" t="str">
-        <v>August 11 livestream: depression and bipolar disorder untreated &gt;15 years — eased within thirty minutes with no recurrence reported.</v>
+        <v>September 11 livestream: severe schizophrenia; malignant alters steering life — within one hour attached spirits were heavily suppressed and symptoms eased, with continued easing over the following month.</v>
       </c>
       <c r="E6" t="str">
-        <v>八月十一日直播间：超过十五年未治愈的抑郁，双向---在三十分钟内缓解并且再无复发</v>
+        <v>九月十一日直播间：严重精分患者，体内的恶性人格操纵人生----- 一小时内附体鬼魂被重度抑制，症状得到缓解，并在之后一个月内持续缓解。</v>
       </c>
       <c r="F6" t="str">
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>achievementsReport.case.2</v>
+        <v>achievementsReport.case.4</v>
       </c>
       <c r="B7" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -559,21 +548,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D7" t="str">
-        <v>June 14 livestream: long-standing PTSD — fully cleared in one spirit (ghost) regulation session; trauma residue dissipated.</v>
+        <v>July 18 livestream: child with autism many years — after harmonizing spirits in the body, symptoms began to improve.</v>
       </c>
       <c r="E7" t="str">
-        <v>六月十四日直播间：困扰多年的PTSD---在一次鬼魂控制中就得到了完全疏通，心灵创伤消散</v>
+        <v>七月十八日直播间：多年自闭症儿童---在调解完体内的灵体后，症状开始改善</v>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>achievementsReport.case.3</v>
+        <v>achievementsReport.case.5</v>
       </c>
       <c r="B8" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -582,44 +571,44 @@
         <v>paragraph / other</v>
       </c>
       <c r="D8" t="str">
-        <v>September 11 livestream: severe schizophrenia; malignant alters steering life — within one hour attached spirits were heavily suppressed and symptoms eased, with continued easing over the following month.</v>
+        <v>September 3 livestream: severe somatization — after using livestream energy work to suppress spirits in the home, somatization and mood greatly improved.</v>
       </c>
       <c r="E8" t="str">
-        <v>九月十一日直播间：严重精分患者，体内的恶性人格操纵人生----- 一小时内附体鬼魂被重度抑制，症状得到缓解，并在之后一个月内持续缓解。</v>
+        <v>九月三日直播间：身上有重度躯体化症状的患者----经过使用直播间能量抑制房屋内鬼魂，躯体化症状大大改善，情绪状况改善。</v>
       </c>
       <c r="F8" t="str">
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>achievementsReport.case.4</v>
+        <v>achievementsReport.cases.title</v>
       </c>
       <c r="B9" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C9" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D9" t="str">
-        <v>July 18 livestream: child with autism many years — after harmonizing spirits in the body, symptoms began to improve.</v>
+        <v>Representative case notes</v>
       </c>
       <c r="E9" t="str">
-        <v>七月十八日直播间：多年自闭症儿童---在调解完体内的灵体后，症状开始改善</v>
+        <v>代表性案例举例</v>
       </c>
       <c r="F9" t="str">
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>achievementsReport.case.5</v>
+        <v>achievementsReport.closing.eyebrow</v>
       </c>
       <c r="B10" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -628,44 +617,47 @@
         <v>paragraph / other</v>
       </c>
       <c r="D10" t="str">
-        <v>September 3 livestream: severe somatization — after using livestream energy work to suppress spirits in the home, somatization and mood greatly improved.</v>
+        <v>A shared horizon</v>
       </c>
       <c r="E10" t="str">
-        <v>九月三日直播间：身上有重度躯体化症状的患者----经过使用直播间能量抑制房屋内鬼魂，躯体化症状大大改善，情绪状况改善。</v>
+        <v>同道之召</v>
       </c>
       <c r="F10" t="str">
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>achievementsReport.i18n.ts</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
       <c r="A11" t="str">
-        <v>achievementsReport.cases.title</v>
+        <v>achievementsReport.closing.invitation</v>
       </c>
       <c r="B11" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C11" t="str">
-        <v>heading</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Representative case notes</v>
-      </c>
-      <c r="E11" t="str">
-        <v>代表性案例举例</v>
+        <v>paragraph / other</v>
+      </c>
+      <c r="D11" t="str" xml:space="preserve">
+        <v xml:space="preserve">**First** improve your own pain and experience the existence of other members' super powers
+— **And then** apply for PRCASG superpowers</v>
+      </c>
+      <c r="E11" t="str" xml:space="preserve">
+        <v xml:space="preserve">**先改善自己的痛苦**,体验其他会员PRCASG超能力的存在
+----**然后**也申请自己拥有PRCASG超能力
+</v>
       </c>
       <c r="F11" t="str">
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>achievementsReport.closing.eyebrow</v>
+        <v>achievementsReport.closing.linksIntro</v>
       </c>
       <c r="B12" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -674,21 +666,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D12" t="str">
-        <v>A shared horizon</v>
+        <v>Original video playback and daily live broadcast summary record of 2025 live broadcast room</v>
       </c>
       <c r="E12" t="str">
-        <v>同道之召</v>
+        <v>2025直播间原始视频回放和每日直播摘要记录</v>
       </c>
       <c r="F12" t="str">
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
+        <v>achievementsReport.i18n.ts</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="str">
-        <v>achievementsReport.closing.invitation</v>
+        <v>achievementsReport.closing.miracle</v>
       </c>
       <c r="B13" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -696,24 +688,22 @@
       <c r="C13" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D13" t="str" xml:space="preserve">
-        <v xml:space="preserve">**You can gain the same capacities** written into this report — what you have just reviewed is **trainable**, not the private gift of a single family.
-Remote control, **Master Spirit**–coordinated spirit regulation, and the relief windows you saw in the data are **replicable** on ASRA’s path. Step across the threshold: **the lineage is open, and the work is meant for you.**</v>
-      </c>
-      <c r="E13" t="str" xml:space="preserve">
-        <v xml:space="preserve">**你也能获得同样的能力**——你在本篇读到的**远程控制**、**高级控制灵协同下的鬼魂管理**与那些**可度量的缓解窗口**，都不是极少数人的私藏，而是**可训练、可复现**的路径。
-在 **ASRA** 的系统修习中，这些程序会被**有序地交到你的手中**。**这份能力，同样为你预备。**</v>
+      <c r="D13" t="str">
+        <v>You were not shown miracles in order to remain only a spectator.</v>
+      </c>
+      <c r="E13" t="str">
+        <v>这些奇迹不仅仅是让你作为一个旁观者</v>
       </c>
       <c r="F13" t="str">
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>achievementsReport.i18n.ts</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
       <c r="A14" t="str">
-        <v>achievementsReport.closing.linksIntro</v>
+        <v>achievementsReport.cohort.body</v>
       </c>
       <c r="B14" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -721,45 +711,47 @@
       <c r="C14" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D14" t="str">
-        <v>Public record — sessions &amp; archive:</v>
-      </c>
-      <c r="E14" t="str">
-        <v>公开留痕 — 直播间与回放列表：</v>
+      <c r="D14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nearly all participants were **treatment-resistant**, **refractory** cases.
+They entered via **TikTok recommendations**, took a **"free trial"** posture, and followed: **remote attached-spirit management** → **dialogue** → **spirit (ghost) regulation** → **reported improvement**.</v>
+      </c>
+      <c r="E14" t="str" xml:space="preserve">
+        <v xml:space="preserve">接受鬼魂控制者**绝大多数**为**耐药性难治**案例。
+经 **TikTok** 随机推荐入场，持**试一试**心态，流程为：**远程附体唤出 → 与鬼魂交流 → 鬼魂控制 → 状态改善**。</v>
       </c>
       <c r="F14" t="str">
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>achievementsReport.closing.miracle</v>
+        <v>achievementsReport.cohort.title</v>
       </c>
       <c r="B15" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C15" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D15" t="str">
-        <v>You were not shown miracles in order to remain only a spectator.</v>
+        <v>Sources of improved participants and basic workflow</v>
       </c>
       <c r="E15" t="str">
-        <v>这些奇迹不仅仅是让你作为一个旁观者</v>
+        <v>被改善者来源和基本流程</v>
       </c>
       <c r="F15" t="str">
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
-      </c>
-    </row>
-    <row r="16" xml:space="preserve">
+        <v>achievementsReport.i18n.ts</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="str">
-        <v>achievementsReport.cohort.body</v>
+        <v>achievementsReport.contents</v>
       </c>
       <c r="B16" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -767,47 +759,45 @@
       <c r="C16" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Nearly all participants were **treatment-resistant**, **refractory** cases.
-They entered via **TikTok recommendations**, took a **“free trial”** posture, and followed: **remote attached-spirit management** → **dialogue** → **spirit (ghost) regulation** → **reported improvement**.</v>
-      </c>
-      <c r="E16" t="str" xml:space="preserve">
-        <v xml:space="preserve">接受鬼魂控制者**绝大多数**为**耐药性难治**案例。
-经 **TikTok** 随机推荐入场，持**试一试**心态，流程为：**远程附体唤出 → 与鬼魂交流 → 鬼魂控制 → 状态改善**。</v>
+      <c r="D16" t="str">
+        <v>Contents</v>
+      </c>
+      <c r="E16" t="str">
+        <v>目录</v>
       </c>
       <c r="F16" t="str">
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>achievementsReport.cohort.title</v>
+        <v>achievementsReport.exp.1</v>
       </c>
       <c r="B17" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C17" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D17" t="str">
-        <v>Sources of improved participants and basic workflow</v>
+        <v>Rapid cross-conversion among mood-disorder, schizophrenia, and DID symptoms within a short interval.</v>
       </c>
       <c r="E17" t="str">
-        <v>被改善者来源和基本流程</v>
+        <v>短时间内将情绪障碍，精分，DID症状互相转换</v>
       </c>
       <c r="F17" t="str">
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>achievementsReport.contents</v>
+        <v>achievementsReport.exp.2</v>
       </c>
       <c r="B18" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -816,21 +806,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D18" t="str">
-        <v>Contents</v>
+        <v>Attached spirit (ghost) somatic relocation vs. host symptom improvement — mapping.</v>
       </c>
       <c r="E18" t="str">
-        <v>目录</v>
+        <v>附体鬼魂躯体移动，宿主症状改善</v>
       </c>
       <c r="F18" t="str">
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>achievementsReport.dist.body</v>
+        <v>achievementsReport.exp.3</v>
       </c>
       <c r="B19" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -839,21 +829,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D19" t="str">
-        <v>**Figures and replay-linked media** are maintained for transparency; **cohort identities are anonymized**.+</v>
+        <v>Experimental external application of medication.</v>
       </c>
       <c r="E19" t="str">
-        <v>**图示与回放链接**用于**透明留痕**；**队列身份均匿名**。</v>
+        <v>药物的体外应用实验</v>
       </c>
       <c r="F19" t="str">
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>achievementsReport.dist.title</v>
+        <v>achievementsReport.exp.title</v>
       </c>
       <c r="B20" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -862,21 +852,21 @@
         <v>heading</v>
       </c>
       <c r="D20" t="str">
-        <v>Distribution &amp; documentation</v>
+        <v>Research-style procedures in the livestream</v>
       </c>
       <c r="E20" t="str">
-        <v>分发说明与资料来源</v>
+        <v>直播间进行的科研实验</v>
       </c>
       <c r="F20" t="str">
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>achievementsReport.exp.1</v>
+        <v>achievementsReport.hero.caption</v>
       </c>
       <c r="B21" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -885,21 +875,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D21" t="str">
-        <v>(1) Rapid cross-conversion among mood-disorder, schizophrenia, and DID symptoms within a short interval.</v>
+        <v>President of ASRA ,Caros woo</v>
       </c>
       <c r="E21" t="str">
-        <v>1.短时间内将情绪障碍，精分，DID症状互相转换</v>
+        <v>ASRA会长  Caros Woo</v>
       </c>
       <c r="F21" t="str">
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>achievementsReport.exp.2</v>
+        <v>achievementsReport.interesting.1</v>
       </c>
       <c r="B22" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -908,21 +898,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D22" t="str">
-        <v>(2) Attached spirit (ghost) somatic relocation vs. host symptom improvement — mapping.</v>
+        <v>Oldest spirits (ghosts): a sibling pair who died in the Quebec region in 1813, still retaining full memories.</v>
       </c>
       <c r="E22" t="str">
-        <v>2.附体鬼魂躯体移动，宿主症状改善</v>
+        <v>年龄最大鬼魂：一对死于1813年魁北克地区的兄妹灵体，至今仍保留着完整记忆</v>
       </c>
       <c r="F22" t="str">
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>achievementsReport.exp.3</v>
+        <v>achievementsReport.interesting.2</v>
       </c>
       <c r="B23" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -931,44 +921,44 @@
         <v>paragraph / other</v>
       </c>
       <c r="D23" t="str">
-        <v>(3) Experimental external application of medication.</v>
+        <v>Non-human parasitic spirit (ghost): a spirit once parasitized a horse, then moved to the horse’s caretaker, allowing equine emotion and awareness to transfer in part to the host.</v>
       </c>
       <c r="E23" t="str">
-        <v>3.药物的体外应用实验</v>
+        <v>非人类寄生鬼魂：一名灵体曾寄生过马匹，并且后来转移到饲养员身上，使得能够将马的部分情绪和意识传递给饲养员</v>
       </c>
       <c r="F23" t="str">
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>achievementsReport.exp.title</v>
+        <v>achievementsReport.interesting.3</v>
       </c>
       <c r="B24" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C24" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D24" t="str">
-        <v>Research-style procedures in the livestream</v>
+        <v>Strongest PSI-type spirit (ghost): could produce scars on the host’s body, move blankets, and create numerous luminous orbs flying through the home.</v>
       </c>
       <c r="E24" t="str">
-        <v>直播间进行的科研实验</v>
+        <v>PSI能力最强的鬼魂：能够直接在宿主身上制造伤痕，并且移动被子，在家中制造大量飞舞的光球</v>
       </c>
       <c r="F24" t="str">
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>achievementsReport.hero.caption</v>
+        <v>achievementsReport.interesting.4</v>
       </c>
       <c r="B25" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -977,21 +967,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D25" t="str">
-        <v>Figure 1</v>
+        <v>Most RPO (remote port organ) coverage: RPOs on all five members of one household, affecting the whole family line.</v>
       </c>
       <c r="E25" t="str">
-        <v>图1</v>
+        <v>拥有最多RPO（remote port organ）的鬼魂：在一家五口身上都有RPO，影响着整个家族</v>
       </c>
       <c r="F25" t="str">
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>achievementsReport.interesting.1</v>
+        <v>achievementsReport.interesting.5</v>
       </c>
       <c r="B26" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1000,21 +990,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D26" t="str">
-        <v>Oldest spirits (ghosts): a sibling pair who died in the Quebec region in 1813, still retaining full memories.</v>
+        <v>Spirit (ghost) with the most human-like pattern: attached at age ten, appeared, and agreed with the host to take turns controlling the body — enabling travel and career completion.</v>
       </c>
       <c r="E26" t="str">
-        <v>年龄最大鬼魂：一对死于1813年魁北克地区的兄妹灵体，至今仍保留着完整记忆</v>
+        <v>生存模式最接近人类的鬼魂：在宿主十岁时寄生，并且现身，与宿主达成轮流操控身体的协议，帮助宿主周游列国，完成事业</v>
       </c>
       <c r="F26" t="str">
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>achievementsReport.interesting.2</v>
+        <v>achievementsReport.interesting.6</v>
       </c>
       <c r="B27" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1023,21 +1013,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D27" t="str">
-        <v>Non-human parasitic spirit (ghost): a spirit once parasitized a horse, then moved to the horse’s caretaker, allowing equine emotion and awareness to transfer in part to the host.</v>
+        <v>Youngest spirit (ghost): estimated at five years of age.</v>
       </c>
       <c r="E27" t="str">
-        <v>非人类寄生鬼魂：一名灵体曾寄生过马匹，并且后来转移到饲养员身上，使得能够将马的部分情绪和意识传递给饲养员</v>
+        <v>年龄最小的鬼魂：只有五岁</v>
       </c>
       <c r="F27" t="str">
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>achievementsReport.interesting.3</v>
+        <v>achievementsReport.interesting.7</v>
       </c>
       <c r="B28" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1046,21 +1036,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D28" t="str">
-        <v>Strongest PSI-type spirit (ghost): could produce scars on the host’s body, move blankets, and create numerous luminous orbs flying through the home.</v>
+        <v>Romance and break-up between spirits (ghosts): two attached spirits in the same host could fall in love, interact in awareness, and break up.</v>
       </c>
       <c r="E28" t="str">
-        <v>PSI能力最强的鬼魂：能够直接在宿主身上制造伤痕，并且移动被子，在家中制造大量飞舞的光球</v>
+        <v>鬼魂之间的恋爱与分手：两名在同一宿主身内的附体鬼魂能够陷入恋爱，进行意识交互以及分手</v>
       </c>
       <c r="F28" t="str">
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>achievementsReport.interesting.4</v>
+        <v>achievementsReport.interesting.intro</v>
       </c>
       <c r="B29" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1069,44 +1059,44 @@
         <v>paragraph / other</v>
       </c>
       <c r="D29" t="str">
-        <v>Most RPO (remote port organ) coverage: RPOs on all five members of one household, affecting the whole family line.</v>
+        <v>Among attached spirits, many profiles are **especially vivid ，rich &amp; interesting**; a **selection** follows:</v>
       </c>
       <c r="E29" t="str">
-        <v>拥有最多RPO（remote port organ）的鬼魂：在一家五口身上都有RPO，影响着整个家族</v>
+        <v>在众多附体鬼魂中，有多例**丰富有趣**的案例；此处**择要**陈列：</v>
       </c>
       <c r="F29" t="str">
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>achievementsReport.interesting.5</v>
+        <v>achievementsReport.interesting.title</v>
       </c>
       <c r="B30" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C30" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D30" t="str">
-        <v>Spirit (ghost) with the most human-like pattern: attached at age ten, appeared, and agreed with the host to take turns controlling the body — enabling travel and career completion.</v>
+        <v>Especially notable spirits (ghosts) in livestream</v>
       </c>
       <c r="E30" t="str">
-        <v>生存模式最接近人类的鬼魂：在宿主十岁时寄生，并且现身，与宿主达成轮流操控身体的协议，帮助宿主周游列国，完成事业</v>
+        <v>直播间中特别有趣的鬼魂</v>
       </c>
       <c r="F30" t="str">
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>achievementsReport.interesting.6</v>
+        <v>achievementsReport.master.1</v>
       </c>
       <c r="B31" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1115,21 +1105,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D31" t="str">
-        <v>Youngest spirit (ghost): estimated at five years of age.</v>
+        <v>July 31 livestream: host mkanimalsea and the attached spirit (ghost) summoned a huge, black, rapidly moving archangel.</v>
       </c>
       <c r="E31" t="str">
-        <v>年龄最小的鬼魂：只有五岁</v>
+        <v>七月三十一日直播间，宿主mkanimalsea和身上的附体鬼魂召唤到了巨大，黑色，移动迅速的大天使。</v>
       </c>
       <c r="F31" t="str">
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>achievementsReport.interesting.7</v>
+        <v>achievementsReport.master.2</v>
       </c>
       <c r="B32" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1138,21 +1128,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D32" t="str">
-        <v>Romance and break-up between spirits (ghosts): two attached spirits in the same host could fall in love, interact in awareness, and break up.</v>
+        <v>July 25 livestream: two attached spirits ghosts on the host jen used a spell to summon the master spirit. For the arrival of the master spirit, one attached spirit ghost feels the guiding spirit with light and love, and the other attached spirit ghost feels the dark knight</v>
       </c>
       <c r="E32" t="str">
-        <v>鬼魂之间的恋爱与分手：两名在同一宿主身内的附体鬼魂能够陷入恋爱，进行意识交互以及分手</v>
+        <v>七月二十五日直播间，宿主jen身上的两名附体鬼魂在使用咒语召唤高级控制灵后。对于到来的高级控制灵，一名附体鬼魂感受到的是带着光和爱的指导灵，另一名附体鬼魂感受到的是黑暗骑士</v>
       </c>
       <c r="F32" t="str">
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>achievementsReport.interesting.intro</v>
+        <v>achievementsReport.master.3</v>
       </c>
       <c r="B33" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1161,21 +1151,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D33" t="str">
-        <v>Among attached spirits, many profiles are **especially vivid**; a **selection** follows:</v>
+        <v>August 14 livestream: host Dominick summoned the arrival and instruction of the divine designation “Elohim.”</v>
       </c>
       <c r="E33" t="str">
-        <v>在众多附体鬼魂中，有多例**形态鲜明**的案例；此处**择要**陈列：</v>
+        <v>八月十四日直播间，宿主dominick召唤到了神灵"elohim"的到来和指示。</v>
       </c>
       <c r="F33" t="str">
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>achievementsReport.interesting.title</v>
+        <v>achievementsReport.master.title</v>
       </c>
       <c r="B34" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1184,44 +1174,44 @@
         <v>heading</v>
       </c>
       <c r="D34" t="str">
-        <v>Especially notable spirits (ghosts)</v>
+        <v>Master Spirit revealance in the livestream</v>
       </c>
       <c r="E34" t="str">
-        <v>特别有趣的鬼魂</v>
+        <v>直播间高级控制灵的现身</v>
       </c>
       <c r="F34" t="str">
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>achievementsReport.master.1</v>
+        <v>achievementsReport.metric.1200.label</v>
       </c>
       <c r="B35" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C35" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D35" t="str">
-        <v>July 31 livestream: host mkanimalsea and the attached spirit (ghost) summoned a huge, black, rapidly moving archangel.</v>
+        <v>In-depth listener interviews</v>
       </c>
       <c r="E35" t="str">
-        <v>七月三十一日直播间，宿主mkanimalsea和身上的附体鬼魂召唤到了巨大，黑色，移动迅速的大天使。</v>
+        <v>深度访谈听众</v>
       </c>
       <c r="F35" t="str">
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>achievementsReport.master.2</v>
+        <v>achievementsReport.metric.1200.val</v>
       </c>
       <c r="B36" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1230,67 +1220,67 @@
         <v>paragraph / other</v>
       </c>
       <c r="D36" t="str">
-        <v>July 25 livestream: on host Jen, two attached spirits (ghosts), after incantations to summon a Master Spirit — one sensed a guiding presence of light and love; the other sensed a dark knight.</v>
+        <v>1,200+</v>
       </c>
       <c r="E36" t="str">
-        <v>七月二十五日直播间，宿主jen身上的两名附体鬼魂在使用咒语召唤master spirit后，一名感受到的是带着光和爱的指导灵，另一名感受到的是黑暗骑士。</v>
+        <v>1200+</v>
       </c>
       <c r="F36" t="str">
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>achievementsReport.master.3</v>
+        <v>achievementsReport.metric.240.label</v>
       </c>
       <c r="B37" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C37" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D37" t="str">
-        <v>August 14 livestream: host Dominick summoned the arrival and instruction of the divine designation “Elohim.”</v>
+        <v>Effective spirit (ghost) management (mental-disorder presentations)</v>
       </c>
       <c r="E37" t="str">
-        <v>八月十四日直播间，宿主dominick召唤到了神灵“elohim”的到来和指示。</v>
+        <v>有效鬼魂控制（精神障碍患者）</v>
       </c>
       <c r="F37" t="str">
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>achievementsReport.master.title</v>
+        <v>achievementsReport.metric.240.val</v>
       </c>
       <c r="B38" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C38" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D38" t="str">
-        <v>Master Spirit revealance in the livestream</v>
+        <v>240+</v>
       </c>
       <c r="E38" t="str">
-        <v>直播间高级控制灵的现身</v>
+        <v>240+</v>
       </c>
       <c r="F38" t="str">
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>achievementsReport.metric.1200.label</v>
+        <v>achievementsReport.metric.265.label</v>
       </c>
       <c r="B39" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1299,21 +1289,21 @@
         <v>heading</v>
       </c>
       <c r="D39" t="str">
-        <v>In-depth listener interviews</v>
+        <v>Public-benefit livestreams (one year)</v>
       </c>
       <c r="E39" t="str">
-        <v>深度访谈听众</v>
+        <v>公益直播（过去一年）</v>
       </c>
       <c r="F39" t="str">
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>achievementsReport.metric.1200.val</v>
+        <v>achievementsReport.metric.265.val</v>
       </c>
       <c r="B40" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1322,21 +1312,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D40" t="str">
-        <v>1,200+</v>
+        <v>255+</v>
       </c>
       <c r="E40" t="str">
-        <v>1200+</v>
+        <v>255+</v>
       </c>
       <c r="F40" t="str">
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>achievementsReport.metric.240.label</v>
+        <v>achievementsReport.metric.400.label</v>
       </c>
       <c r="B41" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1345,21 +1335,21 @@
         <v>heading</v>
       </c>
       <c r="D41" t="str">
-        <v>Effective spirit (ghost) management (mental-disorder presentations)</v>
+        <v>Attached spirits (ghosts) brought forward (some hosts: multiple spirits)</v>
       </c>
       <c r="E41" t="str">
-        <v>有效鬼魂控制（mental disorder 患者）</v>
+        <v>唤出附体鬼魂（部分多灵附体）</v>
       </c>
       <c r="F41" t="str">
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>achievementsReport.metric.240.val</v>
+        <v>achievementsReport.metric.400.val</v>
       </c>
       <c r="B42" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1368,21 +1358,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D42" t="str">
-        <v>240+</v>
+        <v>400+</v>
       </c>
       <c r="E42" t="str">
-        <v>240+</v>
+        <v>400+</v>
       </c>
       <c r="F42" t="str">
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>achievementsReport.metric.265.label</v>
+        <v>achievementsReport.metric.70k.label</v>
       </c>
       <c r="B43" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1391,21 +1381,21 @@
         <v>heading</v>
       </c>
       <c r="D43" t="str">
-        <v>Public-benefit livestreams (one year)</v>
+        <v>Related listeners reached</v>
       </c>
       <c r="E43" t="str">
-        <v>公益直播（过去一年）</v>
+        <v>接触相关听众</v>
       </c>
       <c r="F43" t="str">
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>achievementsReport.metric.265.val</v>
+        <v>achievementsReport.metric.70k.val</v>
       </c>
       <c r="B44" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1414,21 +1404,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D44" t="str">
-        <v>265+</v>
+        <v>70,000+</v>
       </c>
       <c r="E44" t="str">
-        <v>265+</v>
+        <v>70000+</v>
       </c>
       <c r="F44" t="str">
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>achievementsReport.metric.400.label</v>
+        <v>achievementsReport.metric.800.label</v>
       </c>
       <c r="B45" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1437,21 +1427,21 @@
         <v>heading</v>
       </c>
       <c r="D45" t="str">
-        <v>Attached spirits (ghosts) brought forward (some hosts: multiple spirits)</v>
+        <v>Total live airtime (hours)</v>
       </c>
       <c r="E45" t="str">
-        <v>唤出附体鬼魂（部分多灵附体）</v>
+        <v>总直播时长（小时）</v>
       </c>
       <c r="F45" t="str">
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>achievementsReport.metric.400.val</v>
+        <v>achievementsReport.metric.800.val</v>
       </c>
       <c r="B46" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1460,44 +1450,44 @@
         <v>paragraph / other</v>
       </c>
       <c r="D46" t="str">
-        <v>400+</v>
+        <v>800+</v>
       </c>
       <c r="E46" t="str">
-        <v>400+</v>
+        <v>800+</v>
       </c>
       <c r="F46" t="str">
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>achievementsReport.metric.70k.label</v>
+        <v>achievementsReport.orgLine</v>
       </c>
       <c r="B47" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C47" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D47" t="str">
-        <v>Related listeners reached</v>
+        <v>Spirit Ambassador Association (ASra)</v>
       </c>
       <c r="E47" t="str">
-        <v>接触相关听众</v>
+        <v>灵魂世界使者协会（ASRA）</v>
       </c>
       <c r="F47" t="str">
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>achievementsReport.i18n.ts</v>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
       <c r="A48" t="str">
-        <v>achievementsReport.metric.70k.val</v>
+        <v>achievementsReport.outcomes.body</v>
       </c>
       <c r="B48" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1505,22 +1495,24 @@
       <c r="C48" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D48" t="str">
-        <v>70,000+</v>
-      </c>
-      <c r="E48" t="str">
-        <v>70000+</v>
+      <c r="D48" t="str" xml:space="preserve">
+        <v xml:space="preserve">**&gt;80%** of human hosts and attached spirits (ghosts) both reported **complete relief** of acute mental distress (spirits in this cohort also showed **mental-disorder–like states**).
+Through **24 December 2025**, **most**improved patients did not request a **second round** of regulation — i.e. **no relapse** in that window **by self-report**.</v>
+      </c>
+      <c r="E48" t="str" xml:space="preserve">
+        <v xml:space="preserve">**&gt;80%** 的人类宿主与附体鬼魂双方**自觉**各类精神痛苦**显著缓解**（鬼魂侧亦常伴**精神障碍样**表现）。
+改善后至 **2025 年 12 月 24 日**，改善者**多数**未再要求**二次鬼魂控制**，即**自述**该时段内**无复发**。</v>
       </c>
       <c r="F48" t="str">
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>achievementsReport.metric.800.label</v>
+        <v>achievementsReport.outcomes.title</v>
       </c>
       <c r="B49" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1529,21 +1521,21 @@
         <v>heading</v>
       </c>
       <c r="D49" t="str">
-        <v>Total live airtime (hours)</v>
+        <v>Direct effects</v>
       </c>
       <c r="E49" t="str">
-        <v>总直播时长（小时）</v>
+        <v>直接效果</v>
       </c>
       <c r="F49" t="str">
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>achievementsReport.i18n.ts</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
       <c r="A50" t="str">
-        <v>achievementsReport.metric.800.val</v>
+        <v>achievementsReport.s1.lead</v>
       </c>
       <c r="B50" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1551,22 +1543,24 @@
       <c r="C50" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D50" t="str">
-        <v>800+</v>
-      </c>
-      <c r="E50" t="str">
-        <v>800+</v>
+      <c r="D50" t="str" xml:space="preserve">
+        <v xml:space="preserve">From February to December, 2025, Caros conducted 255+ recorded public service live broadcast on TikTok, with a total duration of more than 800 hours. Tiktok pushes 70,000+ high-related people to visit the live broadcast room; In-depth interviews with 1,200+ people; Among them, summon 400+ attached spirits ghosts hidden in patients for many years and communicate with them deeply. Help 240+ patients with mental disorders quickly improve the pain caused by attached spirits ghosts on the spot.
+Roughly **70,000+** related listeners were reached; more than **1,200+** extended interviews; **effective spirit (ghost) regulation** reached **240+** individuals with mental-disorder presentations; about **400+** attached spirits/ghosts were brought forward (**some hosts carried multiple spirits**).</v>
+      </c>
+      <c r="E50" t="str" xml:space="preserve">
+        <v xml:space="preserve">在2025年2月至12月, Caros在TikTok 上进行了255+有记录的公益直播，总时长超过 800 小时。Tiktok推送70,000+高相关人士来访直播间；与1,200+人次深度访谈；
+其中，召唤400+隐藏在患者体内多年的附体鬼魂并与他们深度交流。帮助240+精神障碍患者现场快速改善附体鬼魂带来的痛苦</v>
       </c>
       <c r="F50" t="str">
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>achievementsReport.metricTable.title</v>
+        <v>achievementsReport.s1.spiritHeading</v>
       </c>
       <c r="B51" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1575,21 +1569,21 @@
         <v>heading</v>
       </c>
       <c r="D51" t="str">
-        <v>Headline quantities (one-year window)</v>
+        <v>Livestream statistics on the lived state of American spirits (ghosts)</v>
       </c>
       <c r="E51" t="str">
-        <v>核心数据（一年窗口）</v>
+        <v>直播间对美国鬼魂生存状态统计</v>
       </c>
       <c r="F51" t="str">
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>achievementsReport.i18n.ts</v>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
       <c r="A52" t="str">
-        <v>achievementsReport.orgLine</v>
+        <v>achievementsReport.s1.spiritIntro</v>
       </c>
       <c r="B52" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1597,70 +1591,70 @@
       <c r="C52" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D52" t="str">
-        <v>Spirit Ambassador Association (ASra)</v>
-      </c>
-      <c r="E52" t="str">
-        <v>灵魂世界使者协会（ASRA）</v>
+      <c r="D52" t="str" xml:space="preserve">
+        <v xml:space="preserve">In the livestream context president caros collected **baseline information** from American spirits (ghosts) across **memory**, **mental state**, **living conditions**, the **death transition**, and **awareness of the spirit world**.
+The summaries below condense repeat patterns voiced across sessions.</v>
+      </c>
+      <c r="E52" t="str" xml:space="preserve">
+        <v xml:space="preserve">会长caros在直播间就美国鬼魂的**记忆**、**精神状态**、**生存状态**、**死亡过程**以及对**灵魂世界**的认知等，做了**全方位基本信息**汇总。
+下列条目是多场会话中**重复出现的模式**的凝练。</v>
       </c>
       <c r="F52" t="str">
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
-      </c>
-    </row>
-    <row r="53" xml:space="preserve">
+        <v>achievementsReport.i18n.ts</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" t="str">
-        <v>achievementsReport.outcomes.body</v>
+        <v>achievementsReport.s1.title</v>
       </c>
       <c r="B53" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C53" t="str">
-        <v>paragraph / other</v>
-      </c>
-      <c r="D53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Within **30 minutes**, **&gt;80%** of human hosts and attached spirits (ghosts) reported **complete relief** of acute mental distress (spirits in this cohort also showed **mental-disorder–like states**).
-Through **24 December 2025**, **most** did not request a **second round** of regulation — i.e. **no relapse** in that window **by self-report**.</v>
-      </c>
-      <c r="E53" t="str" xml:space="preserve">
-        <v xml:space="preserve">**30 分钟内**，**&gt;80%** 的人类宿主与附体鬼魂**自觉**各类精神痛苦**显著缓解**（鬼魂侧亦常伴**精神障碍样**表现）。
-改善后至 **2025 年 12 月 24 日**，**多数**未再要求**二次鬼魂控制**，即**自述**该时段内**无复发**。</v>
+        <v>heading</v>
+      </c>
+      <c r="D53" t="str">
+        <v>I. Data overview</v>
+      </c>
+      <c r="E53" t="str">
+        <v>第一板块：数据概览</v>
       </c>
       <c r="F53" t="str">
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>achievementsReport.outcomes.title</v>
+        <v>achievementsReport.s2.condNote</v>
       </c>
       <c r="B54" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C54" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D54" t="str">
-        <v>Direct effects</v>
+        <v>Tiktok system pushed the following categories of mental patients to the live broadcast room, and their attached spirits ghosts were effectively controlled</v>
       </c>
       <c r="E54" t="str">
-        <v>直接效果</v>
+        <v xml:space="preserve"> Tiktok系统推送了以下类别的精神患者来到直播间，他们身上的鬼魂都得到了有效的控制</v>
       </c>
       <c r="F54" t="str">
         <v/>
       </c>
       <c r="G54" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
-      </c>
-    </row>
-    <row r="55" xml:space="preserve">
+        <v>achievementsReport.i18n.ts</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55" t="str">
-        <v>achievementsReport.s1.lead</v>
+        <v>achievementsReport.s2.intro</v>
       </c>
       <c r="B55" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1668,47 +1662,45 @@
       <c r="C55" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D55" t="str" xml:space="preserve">
-        <v xml:space="preserve">In just the past year, on **TikTok Live**, with **anonymous**, **randomly presenting** participants: more than **255+** public-benefit livestreams, with total airtime exceeding **800+ hours**.
-Roughly **70,000+** related listeners were reached; more than **1,200+** extended interviews; **effective spirit (ghost) regulation** reached **240+** individuals with mental-disorder presentations; about **400+** attached spirits/ghosts were brought forward (**some hosts carried multiple spirits**).</v>
-      </c>
-      <c r="E55" t="str" xml:space="preserve">
-        <v xml:space="preserve">仅仅过去一年、**TikTok 线上直播**、**匿名**、**随机**到访者：**超过 265 场**公益直播，总时长**超过 800 小时**。
-约 **70000+** 触达；与 **1200+** 名听众**深度访谈**；**有效鬼魂控制**逾 **240 名**各类 **mental disorder** 患者；唤出约 **400 名附体鬼魂**（**部分多灵附体**）。</v>
+      <c r="D55" t="str">
+        <v>Patients  include: **schizophrenia**, **bipolar disorder**, **depression**, **anxiety**, **DID**, **PTSD**, **schizoaffective disorder**, **ADHD**, **OCD**, **social phobia**, **driving phobia**.</v>
+      </c>
+      <c r="E55" t="str">
+        <v>**病种包括**：**精分**，**双向**，**抑郁**，**焦虑**，**多重人格障碍**，**创伤后遗症**，**分裂性情感障碍**，**注意力缺陷综合征**，**强迫症**，**社交恐惧症**，**驾驶恐惧症**。</v>
       </c>
       <c r="F55" t="str">
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>achievementsReport.s1.spiritHeading</v>
+        <v>achievementsReport.s2.sec51</v>
       </c>
       <c r="B56" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C56" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D56" t="str">
-        <v>Livestream statistics on the lived state of American spirits (ghosts)</v>
+        <v>Condition coverage</v>
       </c>
       <c r="E56" t="str">
-        <v>直播间对美国鬼魂生存状态统计</v>
+        <v>病种覆盖</v>
       </c>
       <c r="F56" t="str">
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
-      </c>
-    </row>
-    <row r="57" xml:space="preserve">
+        <v>achievementsReport.i18n.ts</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57" t="str">
-        <v>achievementsReport.s1.spiritIntro</v>
+        <v>achievementsReport.s2.sec52</v>
       </c>
       <c r="B57" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1716,70 +1708,68 @@
       <c r="C57" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D57" t="str" xml:space="preserve">
-        <v xml:space="preserve">In the livestream context we collected **baseline information** from American spirits (ghosts) across **memory**, **mental state**, **living conditions**, the **death transition**, and **awareness of the spirit world**.
-The summaries below condense repeat patterns voiced across sessions.</v>
-      </c>
-      <c r="E57" t="str" xml:space="preserve">
-        <v xml:space="preserve">我在直播间就美国鬼魂的**记忆**、**精神状态**、**生存状态**、**死亡过程**以及对**灵魂世界**的认知等，做了**全方位基本信息**汇总。
-下列条目是多场会话中**重复出现的模式**的凝练。</v>
+      <c r="D57" t="str">
+        <v>Spirit management process and technology used in livestream</v>
+      </c>
+      <c r="E57" t="str">
+        <v>直播间鬼魂控制流程和使用的技术</v>
       </c>
       <c r="F57" t="str">
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>achievementsReport.s1.title</v>
+        <v>achievementsReport.s2.sec53</v>
       </c>
       <c r="B58" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C58" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D58" t="str">
-        <v>I. Data overview</v>
+        <v>Main outcomes</v>
       </c>
       <c r="E58" t="str">
-        <v>第一板块：数据概览</v>
+        <v>主要结果</v>
       </c>
       <c r="F58" t="str">
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>achievementsReport.s2.condNote</v>
+        <v>achievementsReport.s2.title</v>
       </c>
       <c r="B59" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C59" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D59" t="str">
-        <v>The following conditions were represented among participants who received contact plus effective spirit (ghost) regulation.</v>
+        <v>II. Ordinary attached spirit (ghost) management on mental-disorder  pateints</v>
       </c>
       <c r="E59" t="str">
-        <v>以下病种出现在接受接触并有效鬼魂控制的患者中。</v>
+        <v>第二板块：常规精神障碍患者身上的附体鬼魂控制</v>
       </c>
       <c r="F59" t="str">
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>achievementsReport.s2.intro</v>
+        <v>achievementsReport.s3.lead</v>
       </c>
       <c r="B60" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1788,44 +1778,44 @@
         <v>paragraph / other</v>
       </c>
       <c r="D60" t="str">
-        <v>**Conditions** for which patients underwent contact and effective spirit (ghost) regulation include: **schizophrenia**, **bipolar disorder**, **depression**, **anxiety**, **DID**, **PTSD**, **schizoaffective disorder**, **ADHD**, **OCD**, **social phobia**, **driving phobia**.</v>
+        <v>**Highlighted cases** (selection):</v>
       </c>
       <c r="E60" t="str">
-        <v>接触并**有效鬼魂控制**的患者，**病种包括**：**精分**，**双向**，**抑郁**，**焦虑**，**多重人格障碍**，**创伤后遗症**，**分裂性情感障碍**，**注意力缺陷综合征**，**强迫症**，**社交恐惧症**，**驾驶恐惧症**。</v>
+        <v>**特别案例**（择要）：</v>
       </c>
       <c r="F60" t="str">
         <v/>
       </c>
       <c r="G60" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>achievementsReport.s2.sec51</v>
+        <v>achievementsReport.s3.title</v>
       </c>
       <c r="B61" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C61" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D61" t="str">
-        <v>Condition coverage</v>
+        <v>III. Special illustrative spirit (ghost) regulation cases</v>
       </c>
       <c r="E61" t="str">
-        <v>病种覆盖</v>
+        <v>第三板块：特殊意义鬼魂控制案例展示</v>
       </c>
       <c r="F61" t="str">
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>achievementsReport.s2.sec52</v>
+        <v>achievementsReport.special.1</v>
       </c>
       <c r="B62" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1834,21 +1824,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D62" t="str">
-        <v>Cohort, workflow, and modalities</v>
+        <v>(1) A quasi-DID patient with more than 30 identities ---tiktok user name annabella: A large number of attached spirits ghosts in the same host control each other, make trouble with each other and jointly influence the host. The situation is very complicated</v>
       </c>
       <c r="E62" t="str">
-        <v>队列来源、流程与技术</v>
+        <v>1、身上超过30个身份的DID准患者---tiktok用户名 annabella：同一宿主内大量附体鬼魂之间的相互控制，相互捣乱，共同影响宿主,情况非常复杂</v>
       </c>
       <c r="F62" t="str">
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>achievementsReport.s2.sec53</v>
+        <v>achievementsReport.special.2</v>
       </c>
       <c r="B63" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1857,44 +1847,44 @@
         <v>paragraph / other</v>
       </c>
       <c r="D63" t="str">
-        <v>Outcomes, case notes, and exploratory procedures</v>
+        <v>(2)The survivor who escaped from the cult, tiktok user name gabby--- attached spirit ghost, fully reveals how cults and mediums control people at the spiritual level and affect people's health</v>
       </c>
       <c r="E63" t="str">
-        <v>转归、案例记录与探索性步骤</v>
+        <v>2、从邪教中逃离的幸存者，tiktok用户名 gabby---附体鬼魂完整揭示了邪教，灵媒是如何在灵魂层面控制人，影响人的健康</v>
       </c>
       <c r="F63" t="str">
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>achievementsReport.s2.title</v>
+        <v>achievementsReport.special.3</v>
       </c>
       <c r="B64" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C64" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D64" t="str">
-        <v>II. Routine mental-disorder spirit (ghost) interventions</v>
+        <v>(3) Tiktok, a delusional patient disguised as a devil and a god, user name idk：--- After playing cards, attached spirits ghosts admit that the sacred identities in paranoia are disguised by themselves and do not exist</v>
       </c>
       <c r="E64" t="str">
-        <v>第二板块：常规mental disorder鬼魂控制</v>
+        <v>3、伪装成魔鬼，神明的妄想症患者tiktok用户名 idk：---通过扑克牌实验后，附体鬼魂承认那些妄想症中神圣的身份都是自己伪装的，并不存在</v>
       </c>
       <c r="F64" t="str">
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>achievementsReport.s3.lead</v>
+        <v>achievementsReport.special.4</v>
       </c>
       <c r="B65" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1903,44 +1893,44 @@
         <v>paragraph / other</v>
       </c>
       <c r="D65" t="str">
-        <v>**Highlighted cases** (selection):</v>
+        <v>(4) DID gay tiktok user name dominick: attached spirit ghost explained how to turn the host into a homosexual through years of hard work.</v>
       </c>
       <c r="E65" t="str">
-        <v>**特别案例**（择要）：</v>
+        <v>4、DID同性恋tiktok用户名 dominick：：附体鬼魂阐述了是如何通过多年努力将宿主变为一名同性恋</v>
       </c>
       <c r="F65" t="str">
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>achievementsReport.s3.title</v>
+        <v>achievementsReport.spirit.1</v>
       </c>
       <c r="B66" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C66" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D66" t="str">
-        <v>III. Special illustrative spirit (ghost) regulation cases</v>
+        <v>(1) **90%** of spirits (ghosts) **do not remember** their name, sex, or other basic pre-death information, and **do not remember the death process**.</v>
       </c>
       <c r="E66" t="str">
-        <v>第三板块：特殊意义鬼魂控制案例展示</v>
+        <v>1　**90%** 的鬼魂**不记得**姓名、性别等**基本生前信息**，也**不记得死亡过程**</v>
       </c>
       <c r="F66" t="str">
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>achievementsReport.special.1</v>
+        <v>achievementsReport.spirit.2</v>
       </c>
       <c r="B67" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1949,21 +1939,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D67" t="str">
-        <v>(1) DID spectrum with ≥30 identities — TikTok @annabella: mutual control, mutual influence, and amnesia among many attached spirits in one host.</v>
+        <v>(2) **100%** of American spirits (ghosts) have **lost most former human qualities** and have taken on **new dispositions**.</v>
       </c>
       <c r="E67" t="str">
-        <v>1、身上超过30个身份的DID准患者---tiktok用户名 annabella：同一宿主内大量附体灵体之间的相互控制，影响，失忆，带来的影响</v>
+        <v>2　**100%** 美国鬼魂**失去大部分人性**，并获得**新的秉性**</v>
       </c>
       <c r="F67" t="str">
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>achievementsReport.special.2</v>
+        <v>achievementsReport.spirit.3</v>
       </c>
       <c r="B68" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1972,21 +1962,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D68" t="str">
-        <v>(2) Survivor leaving a high-control group — TikTok @gabby: attached spirits detailed how cults and spirit mediums steer people and health at the spirit level.</v>
+        <v>(3) **100%** of American spirits (ghosts) acquired **new abilities** in the spirit world.</v>
       </c>
       <c r="E68" t="str">
-        <v>2、从邪教中逃离的幸存者，tiktok用户名 gabby---附体灵体完整揭示了邪教，灵媒是如何在灵体层面控制人，影响人的健康</v>
+        <v>3　**100%** 美国鬼魂在灵魂世界获得**新的能力**</v>
       </c>
       <c r="F68" t="str">
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>achievementsReport.special.3</v>
+        <v>achievementsReport.spirit.4</v>
       </c>
       <c r="B69" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -1995,21 +1985,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D69" t="str">
-        <v>(3) Delusion of demons/deities — TikTok @idk: after a structured card experiment, the attached spirit (ghost) admitted those identities were fabrications.</v>
+        <v>(4) The **vast majority** of attached spirits are *helped by Master Spirits**.to attach or leave human host</v>
       </c>
       <c r="E69" t="str">
-        <v>3、伪装成魔鬼，神明的delusion患者tiktok用户名 idk：---通过扑克牌实验后，附体灵体承认那些身份都是自己伪装的，并不存在</v>
+        <v>4　**绝大部分**附体鬼魂由 **高级掌控灵** **搬运附体或离体**</v>
       </c>
       <c r="F69" t="str">
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>achievementsReport.special.4</v>
+        <v>achievementsReport.spirit.5</v>
       </c>
       <c r="B70" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -2018,21 +2008,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D70" t="str">
-        <v>(4) DID with sexuality transformation — TikTok @dominick: the attached spirit (ghost) admitted and described reshaping the host into a gay orientation over years.</v>
+        <v>(5) **100%** of American spirits (ghosts) and their hosts are constrained by **two kinds of prohibitions** in **UMMA’s soul-control system**, so host and spirit **It is forbidden for both sides to communicate the real physiology and living conditions of spirits ghosts**.</v>
       </c>
       <c r="E70" t="str">
-        <v>4、DID同性恋tiktok用户名 dominick：：附体灵体承认，并且阐述了是如何通过多年改造，将宿主变为一名同性恋</v>
+        <v>5　**100%** 美国鬼魂与宿主受 **UMMA** 灵魂控制系统中**两道禁令**约束，**禁止双方交流鬼魂的真实生理、生存状况**</v>
       </c>
       <c r="F70" t="str">
         <v/>
       </c>
       <c r="G70" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>achievementsReport.spirit.1</v>
+        <v>achievementsReport.tech.1</v>
       </c>
       <c r="B71" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -2041,21 +2031,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D71" t="str">
-        <v>(1) **90%** of spirits (ghosts) **do not remember** their name, sex, or other basic pre-death information, and **do not remember the death process**.</v>
+        <v>(1)The patient aims the picture of the mobile phone live broadcast room at his head, chest and back for irradiation.</v>
       </c>
       <c r="E71" t="str">
-        <v>1　**90%** 的鬼魂**不记得**姓名、性别等**基本生前信息**，也**不记得死亡过程**</v>
+        <v>1. 患者将手机直播间画面对准自己的头部、胸部和背部进行照射</v>
       </c>
       <c r="F71" t="str">
         <v/>
       </c>
       <c r="G71" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>achievementsReport.spirit.2</v>
+        <v>achievementsReport.tech.2</v>
       </c>
       <c r="B72" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -2064,44 +2054,44 @@
         <v>paragraph / other</v>
       </c>
       <c r="D72" t="str">
-        <v>(2) **100%** of American spirits (ghosts) have **lost most former human qualities** and have taken on **new dispositions**.</v>
+        <v>(2) **Release incantations** / **prohibition work**.</v>
       </c>
       <c r="E72" t="str">
-        <v>2　**100%** 美国鬼魂**失去大部分人性**，并获得**新的秉性**</v>
+        <v>2. **解除咒语**</v>
       </c>
       <c r="F72" t="str">
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>achievementsReport.spirit.3</v>
+        <v>achievementsReport.tech.title</v>
       </c>
       <c r="B73" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C73" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D73" t="str">
-        <v>(3) **100%** of American spirits (ghosts) acquired **new abilities** in the spirit world.</v>
+        <v>Two PRCASG technologies used in live broadcast room</v>
       </c>
       <c r="E73" t="str">
-        <v>3　**100%** 美国鬼魂在灵魂世界获得**新的能力**</v>
+        <v>直播间使用的两项PRCASG技术</v>
       </c>
       <c r="F73" t="str">
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>achievementsReport.spirit.4</v>
+        <v>achievementsReport.termGloss</v>
       </c>
       <c r="B74" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -2110,21 +2100,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D74" t="str">
-        <v>(4) The **vast majority** of attachments are **transferred by Master Spirits**.</v>
+        <v/>
       </c>
       <c r="E74" t="str">
-        <v>4　**绝大部分**附体由 **master spirit** **搬运**</v>
+        <v/>
       </c>
       <c r="F74" t="str">
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>achievementsReport.spirit.5</v>
+        <v>achievementsReport.th.note</v>
       </c>
       <c r="B75" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -2133,21 +2123,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D75" t="str">
-        <v>(5) **100%** of American spirits (ghosts) and their hosts are constrained by **two kinds of prohibitions** in **UMMA’s soul-control system**, so host and spirit **barely communicate**.</v>
+        <v>Note</v>
       </c>
       <c r="E75" t="str">
-        <v>5　**100%** 美国鬼魂与宿主受 **UMMA** 灵魂控制系统中**两道禁令**约束，**双方几乎无法交流**</v>
+        <v>说明</v>
       </c>
       <c r="F75" t="str">
         <v/>
       </c>
       <c r="G75" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>achievementsReport.tech.1</v>
+        <v>achievementsReport.th.summary</v>
       </c>
       <c r="B76" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -2156,67 +2146,67 @@
         <v>paragraph / other</v>
       </c>
       <c r="D76" t="str">
-        <v>(1) Mobile livestream image aimed at the host’s **head, chest, and back** for **illumination**.</v>
+        <v>Summary</v>
       </c>
       <c r="E76" t="str">
-        <v>1. **直播间**手机画面对准宿主**头部、胸部和背部**进行**照射**</v>
+        <v>内容</v>
       </c>
       <c r="F76" t="str">
         <v/>
       </c>
       <c r="G76" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>achievementsReport.tech.2</v>
+        <v>achievementsReport.title</v>
       </c>
       <c r="B77" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C77" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D77" t="str">
-        <v>(2) **Release incantations** / **prohibition work**.</v>
+        <v>2025 Livestream Achievements</v>
       </c>
       <c r="E77" t="str">
-        <v>2. **解除咒语**</v>
+        <v>2025直播间成就</v>
       </c>
       <c r="F77" t="str">
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>achievementsReport.tech.title</v>
+        <v>achievementsReport.toc.1</v>
       </c>
       <c r="B78" t="str">
         <v>成就长文 / OurAchievementsView</v>
       </c>
       <c r="C78" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D78" t="str">
-        <v>Two livestream techniques (with Master Spirit coordination)</v>
+        <v>I. Data overview</v>
       </c>
       <c r="E78" t="str">
-        <v>直播间使用的两项技术（master spirit配合）</v>
+        <v>第一板块：数据概览</v>
       </c>
       <c r="F78" t="str">
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>achievementsReport.termGloss</v>
+        <v>achievementsReport.toc.2</v>
       </c>
       <c r="B79" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -2225,21 +2215,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D79" t="str">
-        <v/>
+        <v>II. Ordinary attached spirit (ghost) management on mental-disorder  pateints</v>
       </c>
       <c r="E79" t="str">
-        <v>（翻译参考：鬼魂：spirit（ghost））</v>
+        <v>第二板块：常规精神障碍患者身上的附体鬼魂控制</v>
       </c>
       <c r="F79" t="str">
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>achievementsReport.th.indicator</v>
+        <v>achievementsReport.toc.3</v>
       </c>
       <c r="B80" t="str">
         <v>成就长文 / OurAchievementsView</v>
@@ -2248,205 +2238,205 @@
         <v>paragraph / other</v>
       </c>
       <c r="D80" t="str">
-        <v>Indicator</v>
+        <v>III. Special illustrative cases — livestream links</v>
       </c>
       <c r="E80" t="str">
-        <v>指标</v>
+        <v>第三板块：特殊意义鬼魂控制案例展示</v>
       </c>
       <c r="F80" t="str">
         <v/>
       </c>
       <c r="G80" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>achievementsReport.th.note</v>
+        <v>achievementsPage.backHome</v>
       </c>
       <c r="B81" t="str">
-        <v>成就长文 / OurAchievementsView</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C81" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D81" t="str">
-        <v>Note</v>
+        <v>← Back to Home</v>
       </c>
       <c r="E81" t="str">
-        <v>说明</v>
+        <v>← 返回首页</v>
       </c>
       <c r="F81" t="str">
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>achievementsReport.th.summary</v>
+        <v>achievementsPage.banner.together</v>
       </c>
       <c r="B82" t="str">
-        <v>成就长文 / OurAchievementsView</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C82" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D82" t="str">
-        <v>Summary</v>
+        <v>Behind every figure is a real person seeking relief — and a community of practitioners holding space for change.</v>
       </c>
       <c r="E82" t="str">
-        <v>内容</v>
+        <v>每个数字背后都是在寻求缓解的真实的人——以及为改变托住空间的社群。</v>
       </c>
       <c r="F82" t="str">
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>achievementsReport.th.value</v>
+        <v>achievementsPage.case.cult.body</v>
       </c>
       <c r="B83" t="str">
-        <v>成就长文 / OurAchievementsView</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C83" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D83" t="str">
-        <v>Value</v>
+        <v>An individual exiting coercive group influence and medium-channel imprinting. Intervention targeted residual cultic and “spirit-medium” attachments described as negative spiritual load; subjective clearance of those influences was reported.</v>
       </c>
       <c r="E83" t="str">
-        <v>数值</v>
+        <v>脱离强制性团体影响与灵媒印痕者。干预针对残留的邪教式与“灵媒”附体，描述为负面灵性负荷；报告称主观上已清除。</v>
       </c>
       <c r="F83" t="str">
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>achievementsReport.title</v>
+        <v>achievementsPage.case.cult.title</v>
       </c>
       <c r="B84" t="str">
-        <v>成就长文 / OurAchievementsView</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C84" t="str">
         <v>heading</v>
       </c>
       <c r="D84" t="str">
-        <v>2025 Livestream Achievements</v>
+        <v>Survivor of high-control ideological abuse</v>
       </c>
       <c r="E84" t="str">
-        <v>2025直播间成就</v>
+        <v>高控制意识形态虐待幸存者</v>
       </c>
       <c r="F84" t="str">
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>achievementsReport.toc.1</v>
+        <v>achievementsPage.case.depression.body</v>
       </c>
       <c r="B85" t="str">
-        <v>成就长文 / OurAchievementsView</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C85" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D85" t="str">
-        <v>I. Data overview</v>
+        <v>Long-standing depressive illness without durable relief from conventional routes. A single 30-minute intensive session was associated with reported remission-like relief of mood and energy, with stability maintained afterward without relapse.</v>
       </c>
       <c r="E85" t="str">
-        <v>第一板块：数据概览</v>
+        <v>长年抑郁，常规路径未见持久缓解。单次 30 分钟强化会话后，报告称情绪与精力呈缓解样改善，此后保持稳定、无复发报告。</v>
       </c>
       <c r="F85" t="str">
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>achievementsReport.toc.2</v>
+        <v>achievementsPage.case.depression.title</v>
       </c>
       <c r="B86" t="str">
-        <v>成就长文 / OurAchievementsView</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C86" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D86" t="str">
-        <v>II. Routine mental-disorder cases — spirit (ghost) interventions</v>
+        <v>Treatment-resistant depression (&gt;40 years)</v>
       </c>
       <c r="E86" t="str">
-        <v>第二板块：常规 mental disorder 鬼魂控制</v>
+        <v>难治性抑郁（&gt;40 年）</v>
       </c>
       <c r="F86" t="str">
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>achievementsReport.toc.3</v>
+        <v>achievementsPage.case.did.body</v>
       </c>
       <c r="B87" t="str">
-        <v>成就长文 / OurAchievementsView</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C87" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D87" t="str">
-        <v>III. Special illustrative cases — livestream links</v>
+        <v>A woman with severe dissociative fragmentation (more than thirty distinct identity facets reported). After systematic regulation and internal harmonization, all facets were described as co-existing cooperatively; host-level distress and switching burden were substantially reduced.</v>
       </c>
       <c r="E87" t="str">
-        <v>第三板块：特殊意义鬼魂控制案例展示</v>
+        <v>一名严重分离碎裂的女性（报告三十余个不同身份面向）。经系统调节与内部整合后，各面向被描述为合作共存；宿主痛苦与切换负担显著减轻。</v>
       </c>
       <c r="F87" t="str">
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>achievementsPage.backHome</v>
+        <v>achievementsPage.case.did.title</v>
       </c>
       <c r="B88" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C88" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D88" t="str">
-        <v>← Back to Home</v>
+        <v>DID — 30+ reported identity facets</v>
       </c>
       <c r="E88" t="str">
-        <v>← 返回首页</v>
+        <v>DID — 报告 30+ 身份面向</v>
       </c>
       <c r="F88" t="str">
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>achievementsPage.banner.together</v>
+        <v>achievementsPage.case.psychosis.body</v>
       </c>
       <c r="B89" t="str">
         <v>成就页页脚与说明文案</v>
@@ -2455,205 +2445,205 @@
         <v>paragraph / other</v>
       </c>
       <c r="D89" t="str">
-        <v>Behind every figure is a real person seeking relief — and a community of practitioners holding space for change.</v>
+        <v>A malignant alter / possessory pattern reportedly directing major life decisions. Across roughly one month of layered suppression protocol, the intrusive entity influence was heavily dampened; positive and negative symptoms were reported to fall to a manageable baseline.</v>
       </c>
       <c r="E89" t="str">
-        <v>每个数字背后都是在寻求缓解的真实的人——以及为改变托住空间的社群。</v>
+        <v>报告称恶意他我 / 附体模式主导重大人生决定。约一个月分层抑制后，侵扰性灵体影响大幅减弱；阳性与阴性症状回落至可管理基线。</v>
       </c>
       <c r="F89" t="str">
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>achievementsPage.case.cult.body</v>
+        <v>achievementsPage.case.psychosis.title</v>
       </c>
       <c r="B90" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C90" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D90" t="str">
-        <v>An individual exiting coercive group influence and medium-channel imprinting. Intervention targeted residual cultic and “spirit-medium” attachments described as negative spiritual load; subjective clearance of those influences was reported.</v>
+        <v>Severe schizophrenia with possessory steering</v>
       </c>
       <c r="E90" t="str">
-        <v>脱离强制性团体影响与灵媒印痕者。干预针对残留的邪教式与“灵媒”附体，描述为负面灵性负荷；报告称主观上已清除。</v>
+        <v>重度分裂症伴附体操控</v>
       </c>
       <c r="F90" t="str">
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>achievementsPage.case.cult.title</v>
+        <v>achievementsPage.case.ptsd.body</v>
       </c>
       <c r="B91" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C91" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D91" t="str">
-        <v>Survivor of high-control ideological abuse</v>
+        <v>Decades-long trauma imprint and hypervigilance. One focused regulatory session was described as fully processing the traumatic residue; the participant reported that the trauma “no longer occupied” their lived experience.</v>
       </c>
       <c r="E91" t="str">
-        <v>高控制意识形态虐待幸存者</v>
+        <v>数十年创伤印痕与过度警觉。一次聚焦调节会话后，参与者称创伤残留已“不再占据”其生活体验。</v>
       </c>
       <c r="F91" t="str">
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>achievementsPage.case.depression.body</v>
+        <v>achievementsPage.case.ptsd.title</v>
       </c>
       <c r="B92" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C92" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D92" t="str">
-        <v>Long-standing depressive illness without durable relief from conventional routes. A single 30-minute intensive session was associated with reported remission-like relief of mood and energy, with stability maintained afterward without relapse.</v>
+        <v>Complex PTSD (&gt;33 years)</v>
       </c>
       <c r="E92" t="str">
-        <v>长年抑郁，常规路径未见持久缓解。单次 30 分钟强化会话后，报告称情绪与精力呈缓解样改善，此后保持稳定、无复发报告。</v>
+        <v>复杂性 PTSD（&gt;33 年）</v>
       </c>
       <c r="F92" t="str">
         <v/>
       </c>
       <c r="G92" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>achievementsPage.case.depression.title</v>
+        <v>achievementsPage.case.somatization.body</v>
       </c>
       <c r="B93" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C93" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D93" t="str">
-        <v>Treatment-resistant depression (&gt;40 years)</v>
+        <v>Frequent anomalous activity in the home environment together with intense somatic symptom clusters. Field-level cleansing and attachment suppression paralleled a large reduction in bodily distress and functional limitation.</v>
       </c>
       <c r="E93" t="str">
-        <v>难治性抑郁（&gt;40 年）</v>
+        <v>家中频繁异象伴随强烈躯体症状群。场域级清理与附体抑制并行，身体痛苦与功能受限显著减轻。</v>
       </c>
       <c r="F93" t="str">
         <v/>
       </c>
       <c r="G93" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>achievementsPage.case.did.body</v>
+        <v>achievementsPage.case.somatization.title</v>
       </c>
       <c r="B94" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C94" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D94" t="str">
-        <v>A woman with severe dissociative fragmentation (more than thirty distinct identity facets reported). After systematic regulation and internal harmonization, all facets were described as co-existing cooperatively; host-level distress and switching burden were substantially reduced.</v>
+        <v>Residential field disturbance + severe somatization</v>
       </c>
       <c r="E94" t="str">
-        <v>一名严重分离碎裂的女性（报告三十余个不同身份面向）。经系统调节与内部整合后，各面向被描述为合作共存；宿主痛苦与切换负担显著减轻。</v>
+        <v>住宅场域扰动 + 严重躯体化</v>
       </c>
       <c r="F94" t="str">
         <v/>
       </c>
       <c r="G94" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>achievementsPage.case.did.title</v>
+        <v>achievementsPage.cases.note</v>
       </c>
       <c r="B95" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C95" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D95" t="str">
-        <v>DID — 30+ reported identity facets</v>
+        <v>Condensed, anonymized summaries for readability; identifiers and timelines adjusted to protect privacy.</v>
       </c>
       <c r="E95" t="str">
-        <v>DID — 报告 30+ 身份面向</v>
+        <v>为可读性压缩的匿名摘要；识别信息与时间线已调整以保护隐私。</v>
       </c>
       <c r="F95" t="str">
         <v/>
       </c>
       <c r="G95" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>achievementsPage.case.psychosis.body</v>
+        <v>achievementsPage.cases.title</v>
       </c>
       <c r="B96" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C96" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D96" t="str">
-        <v>A malignant alter / possessory pattern reportedly directing major life decisions. Across roughly one month of layered suppression protocol, the intrusive entity influence was heavily dampened; positive and negative symptoms were reported to fall to a manageable baseline.</v>
+        <v>Highlighted case narratives</v>
       </c>
       <c r="E96" t="str">
-        <v>报告称恶意他我 / 附体模式主导重大人生决定。约一个月分层抑制后，侵扰性灵体影响大幅减弱；阳性与阴性症状回落至可管理基线。</v>
+        <v>重点案例叙事</v>
       </c>
       <c r="F96" t="str">
         <v/>
       </c>
       <c r="G96" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>achievementsPage.case.psychosis.title</v>
+        <v>achievementsPage.closing.body</v>
       </c>
       <c r="B97" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C97" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D97" t="str">
-        <v>Severe schizophrenia with possessory steering</v>
+        <v>The material above is a structured excerpt from a larger field record maintained by the Spirit Ambassador Association (ASra).</v>
       </c>
       <c r="E97" t="str">
-        <v>重度分裂症伴附体操控</v>
+        <v>上文为灵界大使协会（ASra）所保存之较大田野档案的结构化节选。</v>
       </c>
       <c r="F97" t="str">
         <v/>
       </c>
       <c r="G97" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>achievementsPage.case.ptsd.body</v>
+        <v>achievementsPage.closing.body2</v>
       </c>
       <c r="B98" t="str">
         <v>成就页页脚与说明文案</v>
@@ -2662,21 +2652,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D98" t="str">
-        <v>Decades-long trauma imprint and hypervigilance. One focused regulatory session was described as fully processing the traumatic residue; the participant reported that the trauma “no longer occupied” their lived experience.</v>
+        <v>Membership and public channels offer routes for inquiry, collaboration, and continued access to session archives as they are published.</v>
       </c>
       <c r="E98" t="str">
-        <v>数十年创伤印痕与过度警觉。一次聚焦调节会话后，参与者称创伤残留已“不再占据”其生活体验。</v>
+        <v>会员与公开渠道提供咨询、协作及在发布后继续获取会话存档的途径。</v>
       </c>
       <c r="F98" t="str">
         <v/>
       </c>
       <c r="G98" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>achievementsPage.case.ptsd.title</v>
+        <v>achievementsPage.closing.title</v>
       </c>
       <c r="B99" t="str">
         <v>成就页页脚与说明文案</v>
@@ -2685,21 +2675,21 @@
         <v>heading</v>
       </c>
       <c r="D99" t="str">
-        <v>Complex PTSD (&gt;33 years)</v>
+        <v>Ongoing documentation</v>
       </c>
       <c r="E99" t="str">
-        <v>复杂性 PTSD（&gt;33 年）</v>
+        <v>持续性的文档工作</v>
       </c>
       <c r="F99" t="str">
         <v/>
       </c>
       <c r="G99" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>achievementsPage.case.somatization.body</v>
+        <v>achievementsPage.conditions.caption</v>
       </c>
       <c r="B100" t="str">
         <v>成就页页脚与说明文案</v>
@@ -2708,90 +2698,90 @@
         <v>paragraph / other</v>
       </c>
       <c r="D100" t="str">
-        <v>Frequent anomalous activity in the home environment together with intense somatic symptom clusters. Field-level cleansing and attachment suppression paralleled a large reduction in bodily distress and functional limitation.</v>
+        <v>Taxonomy (non-exhaustive)</v>
       </c>
       <c r="E100" t="str">
-        <v>家中频繁异象伴随强烈躯体症状群。场域级清理与附体抑制并行，身体痛苦与功能受限显著减轻。</v>
+        <v>分类（非穷尽）</v>
       </c>
       <c r="F100" t="str">
         <v/>
       </c>
       <c r="G100" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>achievementsPage.case.somatization.title</v>
+        <v>achievementsPage.conditions.list</v>
       </c>
       <c r="B101" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C101" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D101" t="str">
-        <v>Residential field disturbance + severe somatization</v>
+        <v>Major depressive disorder and persistent depressive presentations · Generalized and panic spectrum anxiety · Post-traumatic stress disorder (PTSD) · Schizophrenia spectrum · Schizoaffective disorder · Bipolar spectrum · Dissociative identity disorder (DID) · Social anxiety / social phobia · Driving phobia · Attention-deficit hyperactivity disorder (ADHD) · Obsessive–compulsive disorder (OCD)</v>
       </c>
       <c r="E101" t="str">
-        <v>住宅场域扰动 + 严重躯体化</v>
+        <v>重度抑郁及持续性抑郁表现 · 广泛性焦虑与惊恐谱系 · 创伤后应激障碍（PTSD） · 精神分裂症谱系 · 分裂情感性障碍 · 双相谱系 · 分离性身份障碍（DID） · 社交焦虑 / 社交恐惧 · 驾驶恐惧 · 注意缺陷多动障碍（ADHD） · 强迫症（OCD）</v>
       </c>
       <c r="F101" t="str">
         <v/>
       </c>
       <c r="G101" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>achievementsPage.cases.note</v>
+        <v>achievementsPage.conditions.title</v>
       </c>
       <c r="B102" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C102" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D102" t="str">
-        <v>Condensed, anonymized summaries for readability; identifiers and timelines adjusted to protect privacy.</v>
+        <v>Presentations &amp; condition categories addressed</v>
       </c>
       <c r="E102" t="str">
-        <v>为可读性压缩的匿名摘要；识别信息与时间线已调整以保护隐私。</v>
+        <v>所涉及的主诉与症状类别</v>
       </c>
       <c r="F102" t="str">
         <v/>
       </c>
       <c r="G102" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>achievementsPage.cases.title</v>
+        <v>achievementsPage.ctaJoin</v>
       </c>
       <c r="B103" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C103" t="str">
-        <v>heading</v>
+        <v>button / link</v>
       </c>
       <c r="D103" t="str">
-        <v>Highlighted case narratives</v>
+        <v>Apply / Join</v>
       </c>
       <c r="E103" t="str">
-        <v>重点案例叙事</v>
+        <v>申请 / 加入</v>
       </c>
       <c r="F103" t="str">
         <v/>
       </c>
       <c r="G103" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>achievementsPage.closing.body</v>
+        <v>achievementsPage.disclaimer</v>
       </c>
       <c r="B104" t="str">
         <v>成就页页脚与说明文案</v>
@@ -2800,113 +2790,113 @@
         <v>paragraph / other</v>
       </c>
       <c r="D104" t="str">
-        <v>The material above is a structured excerpt from a larger field record maintained by the Spirit Ambassador Association (ASra).</v>
+        <v>This page describes experiential and session-documented outcomes from a specific spiritual–therapeutic practice. It is not medical advice, not a randomized controlled trial, and does not replace diagnosis or care by licensed professionals. Terminology aligns with common clinical labels for reader orientation only.</v>
       </c>
       <c r="E104" t="str">
-        <v>上文为灵界大使协会（ASra）所保存之较大田野档案的结构化节选。</v>
+        <v>本页描述特定灵性—疗愈实践中基于体验与会话记录的结果。非医疗建议，非随机对照试验，也不能替代持证专业人员的诊断或照护。术语仅借常见临床标签帮助读者理解。</v>
       </c>
       <c r="F104" t="str">
         <v/>
       </c>
       <c r="G104" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>achievementsPage.closing.body2</v>
+        <v>achievementsPage.hero.badge</v>
       </c>
       <c r="B105" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C105" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D105" t="str">
-        <v>Membership and public channels offer routes for inquiry, collaboration, and continued access to session archives as they are published.</v>
+        <v>Field documentation · ASra practice</v>
       </c>
       <c r="E105" t="str">
-        <v>会员与公开渠道提供咨询、协作及在发布后继续获取会话存档的途径。</v>
+        <v>田野记录 · ASra 实践</v>
       </c>
       <c r="F105" t="str">
         <v/>
       </c>
       <c r="G105" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>achievementsPage.closing.title</v>
+        <v>achievementsPage.hero.pill1</v>
       </c>
       <c r="B106" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C106" t="str">
-        <v>heading</v>
+        <v>label</v>
       </c>
       <c r="D106" t="str">
-        <v>Ongoing documentation</v>
+        <v>Anonymized cohort</v>
       </c>
       <c r="E106" t="str">
-        <v>持续性的文档工作</v>
+        <v>匿名队列</v>
       </c>
       <c r="F106" t="str">
         <v/>
       </c>
       <c r="G106" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>achievementsPage.conditions.caption</v>
+        <v>achievementsPage.hero.pill2</v>
       </c>
       <c r="B107" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C107" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D107" t="str">
-        <v>Taxonomy (non-exhaustive)</v>
+        <v>Session-based metrics</v>
       </c>
       <c r="E107" t="str">
-        <v>分类（非穷尽）</v>
+        <v>按会话统计</v>
       </c>
       <c r="F107" t="str">
         <v/>
       </c>
       <c r="G107" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>achievementsPage.conditions.list</v>
+        <v>achievementsPage.hero.pill3</v>
       </c>
       <c r="B108" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C108" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D108" t="str">
-        <v>Major depressive disorder and persistent depressive presentations · Generalized and panic spectrum anxiety · Post-traumatic stress disorder (PTSD) · Schizophrenia spectrum · Schizoaffective disorder · Bipolar spectrum · Dissociative identity disorder (DID) · Social anxiety / social phobia · Driving phobia · Attention-deficit hyperactivity disorder (ADHD) · Obsessive–compulsive disorder (OCD)</v>
+        <v>Cross-realm collaboration</v>
       </c>
       <c r="E108" t="str">
-        <v>重度抑郁及持续性抑郁表现 · 广泛性焦虑与惊恐谱系 · 创伤后应激障碍（PTSD） · 精神分裂症谱系 · 分裂情感性障碍 · 双相谱系 · 分离性身份障碍（DID） · 社交焦虑 / 社交恐惧 · 驾驶恐惧 · 注意缺陷多动障碍（ADHD） · 强迫症（OCD）</v>
+        <v>跨界协作</v>
       </c>
       <c r="F108" t="str">
         <v/>
       </c>
       <c r="G108" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>achievementsPage.conditions.title</v>
+        <v>achievementsPage.hero.subtitle</v>
       </c>
       <c r="B109" t="str">
         <v>成就页页脚与说明文案</v>
@@ -2915,44 +2905,44 @@
         <v>heading</v>
       </c>
       <c r="D109" t="str">
-        <v>Presentations &amp; condition categories addressed</v>
+        <v>A structured summary of anonymized, live-session outcomes coordinated with Master Spirit teams in China and the United States — written in a clinical reporting style for transparency.</v>
       </c>
       <c r="E109" t="str">
-        <v>所涉及的主诉与症状类别</v>
+        <v>对匿名、现场会话结果的结构性摘要，与中美高级灵体团队协同——以临床报告风格撰写以利透明。</v>
       </c>
       <c r="F109" t="str">
         <v/>
       </c>
       <c r="G109" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>achievementsPage.ctaJoin</v>
+        <v>achievementsPage.hero.title</v>
       </c>
       <c r="B110" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C110" t="str">
-        <v>button / link</v>
+        <v>heading</v>
       </c>
       <c r="D110" t="str">
-        <v>Apply / Join</v>
+        <v>Our Achievements in Mental Health Support</v>
       </c>
       <c r="E110" t="str">
-        <v>申请 / 加入</v>
+        <v>我们在心理健康支持中的成果</v>
       </c>
       <c r="F110" t="str">
         <v/>
       </c>
       <c r="G110" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>achievementsPage.disclaimer</v>
+        <v>achievementsPage.phenomenology.body</v>
       </c>
       <c r="B111" t="str">
         <v>成就页页脚与说明文案</v>
@@ -2961,21 +2951,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D111" t="str">
-        <v>This page describes experiential and session-documented outcomes from a specific spiritual–therapeutic practice. It is not medical advice, not a randomized controlled trial, and does not replace diagnosis or care by licensed professionals. Terminology aligns with common clinical labels for reader orientation only.</v>
+        <v>Some participants described luminous or angelic presence and a felt sense of protective arrival. Others reported encounter with the divine designation “Elohim” and received directive guidance, which they associated with a durable uplift in meaning, agency, and overall life stance.</v>
       </c>
       <c r="E111" t="str">
-        <v>本页描述特定灵性—疗愈实践中基于体验与会话记录的结果。非医疗建议，非随机对照试验，也不能替代持证专业人员的诊断或照护。术语仅借常见临床标签帮助读者理解。</v>
+        <v>部分参与者描述光明或天使般的临在与被保护抵达之感。另一些人报告遭遇神圣名号“Elohim”并接受指引，将其与意义感、能动性以及整体人生姿态的持久提升相连。</v>
       </c>
       <c r="F111" t="str">
         <v/>
       </c>
       <c r="G111" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>achievementsPage.hero.badge</v>
+        <v>achievementsPage.phenomenology.title</v>
       </c>
       <c r="B112" t="str">
         <v>成就页页脚与说明文案</v>
@@ -2984,90 +2974,90 @@
         <v>heading</v>
       </c>
       <c r="D112" t="str">
-        <v>Field documentation · ASra practice</v>
+        <v>Phenomenological correlates (late-phase reports)</v>
       </c>
       <c r="E112" t="str">
-        <v>田野记录 · ASra 实践</v>
+        <v>现象学相关（后期报告）</v>
       </c>
       <c r="F112" t="str">
         <v/>
       </c>
       <c r="G112" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>achievementsPage.hero.pill1</v>
+        <v>achievementsPage.replayPlaylist</v>
       </c>
       <c r="B113" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C113" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D113" t="str">
-        <v>Anonymized cohort</v>
+        <v>YouTube replay playlist</v>
       </c>
       <c r="E113" t="str">
-        <v>匿名队列</v>
+        <v>YouTube 回放列表</v>
       </c>
       <c r="F113" t="str">
         <v/>
       </c>
       <c r="G113" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>achievementsPage.hero.pill2</v>
+        <v>achievementsPage.scope.body</v>
       </c>
       <c r="B114" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C114" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D114" t="str">
-        <v>Session-based metrics</v>
+        <v>During approximately the past year of TikTok live broadcasts, participants arrived as anonymous, randomly presenting individuals without prior triage. Each encounter used a consistent initial window of thirty minutes for structured exchange, assessment, and spirit-realm–assisted regulation. Outcomes below combine session documentation with participant self-reports; they are presented to illustrate the breadth of the practice rather than as a substitute for peer-reviewed clinical trials.</v>
       </c>
       <c r="E114" t="str">
-        <v>按会话统计</v>
+        <v>在过去约一年的 TikTok 直播中，参与者以匿名、随机到场的方式进入，无事先分诊。每次接触均使用统一的首个三十分钟窗口，进行结构化交流、评估与灵界辅助调节。下列结果合并了会话记录与参与者自述；旨在展示实践广度，而非替代同行评审临床试验。</v>
       </c>
       <c r="F114" t="str">
         <v/>
       </c>
       <c r="G114" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>achievementsPage.hero.pill3</v>
+        <v>achievementsPage.scope.caption</v>
       </c>
       <c r="B115" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C115" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D115" t="str">
-        <v>Cross-realm collaboration</v>
+        <v>Listening, dignity, and steadiness in every first contact.</v>
       </c>
       <c r="E115" t="str">
-        <v>跨界协作</v>
+        <v>每一次首次接触中的倾听、尊严与稳定。</v>
       </c>
       <c r="F115" t="str">
         <v/>
       </c>
       <c r="G115" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>achievementsPage.hero.subtitle</v>
+        <v>achievementsPage.scope.title</v>
       </c>
       <c r="B116" t="str">
         <v>成就页页脚与说明文案</v>
@@ -3076,21 +3066,21 @@
         <v>heading</v>
       </c>
       <c r="D116" t="str">
-        <v>A structured summary of anonymized, live-session outcomes coordinated with Master Spirit teams in China and the United States — written in a clinical reporting style for transparency.</v>
+        <v>Practice context &amp; methodology</v>
       </c>
       <c r="E116" t="str">
-        <v>对匿名、现场会话结果的结构性摘要，与中美高级灵体团队协同——以临床报告风格撰写以利透明。</v>
+        <v>实践背景与方法</v>
       </c>
       <c r="F116" t="str">
         <v/>
       </c>
       <c r="G116" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>achievementsPage.hero.title</v>
+        <v>achievementsPage.stat1.label</v>
       </c>
       <c r="B117" t="str">
         <v>成就页页脚与说明文案</v>
@@ -3099,21 +3089,21 @@
         <v>heading</v>
       </c>
       <c r="D117" t="str">
-        <v>Our Achievements in Mental Health Support</v>
+        <v>Individuals with mental-health–related presentations engaged through the live program (cumulative, ~one year).</v>
       </c>
       <c r="E117" t="str">
-        <v>我们在心理健康支持中的成果</v>
+        <v>通过直播项目接触到的与精神健康相关表现者（累计，约一年）。</v>
       </c>
       <c r="F117" t="str">
         <v/>
       </c>
       <c r="G117" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>achievementsPage.phenomenology.body</v>
+        <v>achievementsPage.stat1.value</v>
       </c>
       <c r="B118" t="str">
         <v>成就页页脚与说明文案</v>
@@ -3122,21 +3112,21 @@
         <v>paragraph / other</v>
       </c>
       <c r="D118" t="str">
-        <v>Some participants described luminous or angelic presence and a felt sense of protective arrival. Others reported encounter with the divine designation “Elohim” and received directive guidance, which they associated with a durable uplift in meaning, agency, and overall life stance.</v>
+        <v>240+</v>
       </c>
       <c r="E118" t="str">
-        <v>部分参与者描述光明或天使般的临在与被保护抵达之感。另一些人报告遭遇神圣名号“Elohim”并接受指引，将其与意义感、能动性以及整体人生姿态的持久提升相连。</v>
+        <v>240+</v>
       </c>
       <c r="F118" t="str">
         <v/>
       </c>
       <c r="G118" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>achievementsPage.phenomenology.title</v>
+        <v>achievementsPage.stat2.label</v>
       </c>
       <c r="B119" t="str">
         <v>成就页页脚与说明文案</v>
@@ -3145,21 +3135,21 @@
         <v>heading</v>
       </c>
       <c r="D119" t="str">
-        <v>Phenomenological correlates (late-phase reports)</v>
+        <v>Reported rapid, marked improvement in emotional state and overall condition after the first 30-minute structured session.</v>
       </c>
       <c r="E119" t="str">
-        <v>现象学相关（后期报告）</v>
+        <v>在首次 30 分钟结构化会话后，报告情绪与整体状态快速、显著改善。</v>
       </c>
       <c r="F119" t="str">
         <v/>
       </c>
       <c r="G119" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>achievementsPage.replayPlaylist</v>
+        <v>achievementsPage.stat2.value</v>
       </c>
       <c r="B120" t="str">
         <v>成就页页脚与说明文案</v>
@@ -3168,44 +3158,44 @@
         <v>paragraph / other</v>
       </c>
       <c r="D120" t="str">
-        <v>YouTube replay playlist</v>
+        <v>80%+</v>
       </c>
       <c r="E120" t="str">
-        <v>YouTube 回放列表</v>
+        <v>80%+</v>
       </c>
       <c r="F120" t="str">
         <v/>
       </c>
       <c r="G120" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>achievementsPage.scope.body</v>
+        <v>achievementsPage.stat3.label</v>
       </c>
       <c r="B121" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C121" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D121" t="str">
-        <v>During approximately the past year of TikTok live broadcasts, participants arrived as anonymous, randomly presenting individuals without prior triage. Each encounter used a consistent initial window of thirty minutes for structured exchange, assessment, and spirit-realm–assisted regulation. Outcomes below combine session documentation with participant self-reports; they are presented to illustrate the breadth of the practice rather than as a substitute for peer-reviewed clinical trials.</v>
+        <v>A notable subset describe complete symptomatic resolution or long-term stability after a single intensive session, with no recurrence reported to date (participant-described).</v>
       </c>
       <c r="E121" t="str">
-        <v>在过去约一年的 TikTok 直播中，参与者以匿名、随机到场的方式进入，无事先分诊。每次接触均使用统一的首个三十分钟窗口，进行结构化交流、评估与灵界辅助调节。下列结果合并了会话记录与参与者自述；旨在展示实践广度，而非替代同行评审临床试验。</v>
+        <v>值得注意的一部分人称：在一次强化会话后即达症状完全缓解或长期稳定，至今无复发（参与者自述）。</v>
       </c>
       <c r="F121" t="str">
         <v/>
       </c>
       <c r="G121" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>achievementsPage.scope.caption</v>
+        <v>achievementsPage.stat3.value</v>
       </c>
       <c r="B122" t="str">
         <v>成就页页脚与说明文案</v>
@@ -3214,412 +3204,251 @@
         <v>paragraph / other</v>
       </c>
       <c r="D122" t="str">
-        <v>Listening, dignity, and steadiness in every first contact.</v>
+        <v>1×</v>
       </c>
       <c r="E122" t="str">
-        <v>每一次首次接触中的倾听、尊严与稳定。</v>
+        <v>1×</v>
       </c>
       <c r="F122" t="str">
         <v/>
       </c>
       <c r="G122" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>achievementsPage.scope.title</v>
+        <v>achievementsPage.team.body</v>
       </c>
       <c r="B123" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C123" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D123" t="str">
-        <v>Practice context &amp; methodology</v>
+        <v>The interventions summarized here are attributed to coordinated work with a large trans-Pacific Master Spirit collective. Master Spirits function as senior administrators in the Spirit Realm; their role in these sessions was to execute technical regulation, containment, and informational alignment alongside the human-facing dialogue.</v>
       </c>
       <c r="E123" t="str">
-        <v>实践背景与方法</v>
+        <v>此处摘要的干预归因于庞大的跨太平洋高级灵体集体的协同工作。高级灵体是灵界资深管理者；在这些会话中负责与人类对话并行执行技术调控、包容与信息对齐。</v>
       </c>
       <c r="F123" t="str">
         <v/>
       </c>
       <c r="G123" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>achievementsPage.stat1.label</v>
+        <v>achievementsPage.team.body2</v>
       </c>
       <c r="B124" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C124" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D124" t="str">
-        <v>Individuals with mental-health–related presentations engaged through the live program (cumulative, ~one year).</v>
+        <v>In later phases of care, Master Spirits increasingly disclosed presence directly. Each participant received individualized revelatory information appropriate to their trajectory — strengthening continuity between ethereal governance and lived recovery.</v>
       </c>
       <c r="E124" t="str">
-        <v>通过直播项目接触到的与精神健康相关表现者（累计，约一年）。</v>
+        <v>在后期照护中，高级灵体更频繁地直接显露存在。每位参与者获得适合其轨迹的启示性信息——强化灵界治理与现实康复之间的连续性。</v>
       </c>
       <c r="F124" t="str">
         <v/>
       </c>
       <c r="G124" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>achievementsPage.stat1.value</v>
+        <v>achievementsPage.team.title</v>
       </c>
       <c r="B125" t="str">
         <v>成就页页脚与说明文案</v>
       </c>
       <c r="C125" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D125" t="str">
-        <v>240+</v>
+        <v>Master Spirit collaboration (China &amp; United States)</v>
       </c>
       <c r="E125" t="str">
-        <v>240+</v>
+        <v>高级灵体协作（中国与美国）</v>
       </c>
       <c r="F125" t="str">
         <v/>
       </c>
       <c r="G125" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>en.ts / zh.ts</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>achievementsPage.stat2.label</v>
+        <v>achievements2025.livestreamLinkPlaceholders[0].label</v>
       </c>
       <c r="B126" t="str">
-        <v>成就页页脚与说明文案</v>
+        <v>成就页 / 收束区外链</v>
       </c>
       <c r="C126" t="str">
-        <v>heading</v>
+        <v>button / link</v>
       </c>
       <c r="D126" t="str">
-        <v>Reported rapid, marked improvement in emotional state and overall condition after the first 30-minute structured session.</v>
+        <v>YouTube — replay playlist</v>
       </c>
       <c r="E126" t="str">
-        <v>在首次 30 分钟结构化会话后，报告情绪与整体状态快速、显著改善。</v>
+        <v/>
       </c>
       <c r="F126" t="str">
         <v/>
       </c>
       <c r="G126" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>href: https://www.youtube.com/playlist?list=PL-pt7dbiRizs_N5TVfKmj5ptuG15TeQgK</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>achievementsPage.stat2.value</v>
+        <v>achievements2025.livestreamLinkPlaceholders[1].label</v>
       </c>
       <c r="B127" t="str">
-        <v>成就页页脚与说明文案</v>
+        <v>成就页 / 收束区外链</v>
       </c>
       <c r="C127" t="str">
-        <v>paragraph / other</v>
+        <v>button / link</v>
       </c>
       <c r="D127" t="str">
-        <v>80%+</v>
+        <v>TikTok — @ASra field archive (placeholder)</v>
       </c>
       <c r="E127" t="str">
-        <v>80%+</v>
+        <v/>
       </c>
       <c r="F127" t="str">
         <v/>
       </c>
       <c r="G127" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v>href: https://www.tiktok.com/</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>achievementsPage.stat3.label</v>
+        <v>reportHeroFigure.alt</v>
       </c>
       <c r="B128" t="str">
-        <v>成就页页脚与说明文案</v>
+        <v>成就页 / 英雄区配图</v>
       </c>
       <c r="C128" t="str">
-        <v>heading</v>
+        <v>label</v>
       </c>
       <c r="D128" t="str">
-        <v>A notable subset describe complete symptomatic resolution or long-term stability after a single intensive session, with no recurrence reported to date (participant-described).</v>
+        <v>Portrait — program principal</v>
       </c>
       <c r="E128" t="str">
-        <v>值得注意的一部分人称：在一次强化会话后即达症状完全缓解或长期稳定，至今无复发（参与者自述）。</v>
+        <v/>
       </c>
       <c r="F128" t="str">
         <v/>
       </c>
       <c r="G128" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>achievementsPage.stat3.value</v>
+        <v>carouselSlides[0].alt</v>
       </c>
       <c r="B129" t="str">
-        <v>成就页页脚与说明文案</v>
+        <v>成就页 / 轮播占位图</v>
       </c>
       <c r="C129" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D129" t="str">
-        <v>1×</v>
+        <v>TikTok Live session screenshot</v>
       </c>
       <c r="E129" t="str">
-        <v>1×</v>
+        <v/>
       </c>
       <c r="F129" t="str">
         <v/>
       </c>
       <c r="G129" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>achievementsPage.team.body</v>
+        <v>carouselSlides[1].alt</v>
       </c>
       <c r="B130" t="str">
-        <v>成就页页脚与说明文案</v>
+        <v>成就页 / 轮播占位图</v>
       </c>
       <c r="C130" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D130" t="str">
-        <v>The interventions summarized here are attributed to coordinated work with a large trans-Pacific Master Spirit collective. Master Spirits function as senior administrators in the Spirit Realm; their role in these sessions was to execute technical regulation, containment, and informational alignment alongside the human-facing dialogue.</v>
+        <v>TikTok Live session screenshot</v>
       </c>
       <c r="E130" t="str">
-        <v>此处摘要的干预归因于庞大的跨太平洋高级灵体集体的协同工作。高级灵体是灵界资深管理者；在这些会话中负责与人类对话并行执行技术调控、包容与信息对齐。</v>
+        <v/>
       </c>
       <c r="F130" t="str">
         <v/>
       </c>
       <c r="G130" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>achievementsPage.team.body2</v>
+        <v>carouselSlides[2].alt</v>
       </c>
       <c r="B131" t="str">
-        <v>成就页页脚与说明文案</v>
+        <v>成就页 / 轮播占位图</v>
       </c>
       <c r="C131" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D131" t="str">
-        <v>In later phases of care, Master Spirits increasingly disclosed presence directly. Each participant received individualized revelatory information appropriate to their trajectory — strengthening continuity between ethereal governance and lived recovery.</v>
+        <v>TikTok Live session screenshot</v>
       </c>
       <c r="E131" t="str">
-        <v>在后期照护中，高级灵体更频繁地直接显露存在。每位参与者获得适合其轨迹的启示性信息——强化灵界治理与现实康复之间的连续性。</v>
+        <v/>
       </c>
       <c r="F131" t="str">
         <v/>
       </c>
       <c r="G131" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+        <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>achievementsPage.team.title</v>
+        <v>carouselSlides[3].alt</v>
       </c>
       <c r="B132" t="str">
-        <v>成就页页脚与说明文案</v>
+        <v>成就页 / 轮播占位图</v>
       </c>
       <c r="C132" t="str">
-        <v>heading</v>
+        <v>label</v>
       </c>
       <c r="D132" t="str">
-        <v>Master Spirit collaboration (China &amp; United States)</v>
+        <v>TikTok Live session screenshot</v>
       </c>
       <c r="E132" t="str">
-        <v>高级灵体协作（中国与美国）</v>
+        <v/>
       </c>
       <c r="F132" t="str">
         <v/>
       </c>
       <c r="G132" t="str">
-        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>achievements2025.livestreamLinkPlaceholders[0].label</v>
-      </c>
-      <c r="B133" t="str">
-        <v>成就页 / 收束区外链</v>
-      </c>
-      <c r="C133" t="str">
-        <v>button / link</v>
-      </c>
-      <c r="D133" t="str">
-        <v>YouTube — replay playlist</v>
-      </c>
-      <c r="E133" t="str">
-        <v/>
-      </c>
-      <c r="F133" t="str">
-        <v/>
-      </c>
-      <c r="G133" t="str">
-        <v>achievements2025Content — href: https://www.youtube.com/playlist?list=PL-pt7dbiRizs_N5TVfKmj5ptuG15TeQgK</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>achievements2025.livestreamLinkPlaceholders[1].label</v>
-      </c>
-      <c r="B134" t="str">
-        <v>成就页 / 收束区外链</v>
-      </c>
-      <c r="C134" t="str">
-        <v>button / link</v>
-      </c>
-      <c r="D134" t="str">
-        <v>TikTok — @ASra field archive (placeholder)</v>
-      </c>
-      <c r="E134" t="str">
-        <v/>
-      </c>
-      <c r="F134" t="str">
-        <v/>
-      </c>
-      <c r="G134" t="str">
-        <v>achievements2025Content — href: https://www.tiktok.com/</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>reportHeroFigure.alt</v>
-      </c>
-      <c r="B135" t="str">
-        <v>成就页 / 英雄区配图</v>
-      </c>
-      <c r="C135" t="str">
-        <v>label</v>
-      </c>
-      <c r="D135" t="str">
-        <v>Portrait — program principal</v>
-      </c>
-      <c r="E135" t="str">
-        <v/>
-      </c>
-      <c r="F135" t="str">
-        <v/>
-      </c>
-      <c r="G135" t="str">
-        <v>Hero `&lt;img alt&gt;` (caption text = i18n achievementsReport.hero.caption)</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>carouselSlides[0].alt</v>
-      </c>
-      <c r="B136" t="str">
-        <v>成就页 / 轮播占位图</v>
-      </c>
-      <c r="C136" t="str">
-        <v>label</v>
-      </c>
-      <c r="D136" t="str">
-        <v>TikTok Live session screenshot</v>
-      </c>
-      <c r="E136" t="str">
-        <v/>
-      </c>
-      <c r="F136" t="str">
-        <v/>
-      </c>
-      <c r="G136" t="str">
-        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>carouselSlides[1].alt</v>
-      </c>
-      <c r="B137" t="str">
-        <v>成就页 / 轮播占位图</v>
-      </c>
-      <c r="C137" t="str">
-        <v>label</v>
-      </c>
-      <c r="D137" t="str">
-        <v>TikTok Live session screenshot</v>
-      </c>
-      <c r="E137" t="str">
-        <v/>
-      </c>
-      <c r="F137" t="str">
-        <v/>
-      </c>
-      <c r="G137" t="str">
-        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>carouselSlides[2].alt</v>
-      </c>
-      <c r="B138" t="str">
-        <v>成就页 / 轮播占位图</v>
-      </c>
-      <c r="C138" t="str">
-        <v>label</v>
-      </c>
-      <c r="D138" t="str">
-        <v>TikTok Live session screenshot</v>
-      </c>
-      <c r="E138" t="str">
-        <v/>
-      </c>
-      <c r="F138" t="str">
-        <v/>
-      </c>
-      <c r="G138" t="str">
-        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>carouselSlides[3].alt</v>
-      </c>
-      <c r="B139" t="str">
-        <v>成就页 / 轮播占位图</v>
-      </c>
-      <c r="C139" t="str">
-        <v>label</v>
-      </c>
-      <c r="D139" t="str">
-        <v>TikTok Live session screenshot</v>
-      </c>
-      <c r="E139" t="str">
-        <v/>
-      </c>
-      <c r="F139" t="str">
-        <v/>
-      </c>
-      <c r="G139" t="str">
-        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G139"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G132"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/page-copy/07-我们的成就.xlsx
+++ b/docs/page-copy/07-我们的成就.xlsx
@@ -525,7 +525,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D6" t="str">
-        <v>September 11 livestream: severe schizophrenia; malignant alters steering life — within one hour attached spirits were heavily suppressed and symptoms eased, with continued easing over the following month.</v>
+        <v>September 11 livestream: severe schizophrenia; malignant alters steering life — within one hour attached **spirits (ghosts)** were heavily suppressed and symptoms eased, with continued easing over the following month.</v>
       </c>
       <c r="E6" t="str">
         <v>九月十一日直播间：严重精分患者，体内的恶性人格操纵人生----- 一小时内附体鬼魂被重度抑制，症状得到缓解，并在之后一个月内持续缓解。</v>
@@ -548,7 +548,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D7" t="str">
-        <v>July 18 livestream: child with autism many years — after harmonizing spirits in the body, symptoms began to improve.</v>
+        <v>July 18 livestream: child with autism many years — after harmonizing **spirits (ghosts)** in the body, symptoms began to improve.</v>
       </c>
       <c r="E7" t="str">
         <v>七月十八日直播间：多年自闭症儿童---在调解完体内的灵体后，症状开始改善</v>
@@ -571,7 +571,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D8" t="str">
-        <v>September 3 livestream: severe somatization — after using livestream energy work to suppress spirits in the home, somatization and mood greatly improved.</v>
+        <v>September 3 livestream: severe somatization — after using livestream energy work to suppress **spirits (ghosts)** in the home, somatization and mood greatly improved.</v>
       </c>
       <c r="E8" t="str">
         <v>九月三日直播间：身上有重度躯体化症状的患者----经过使用直播间能量抑制房屋内鬼魂，躯体化症状大大改善，情绪状况改善。</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="D14" t="str" xml:space="preserve">
         <v xml:space="preserve">Nearly all participants were treatment-resistant, refractory cases.
-They entered via TikTok recommendations, took a “try it” posture, and followed: remote bring-forward → dialogue → spirit regulation → reported improvement.</v>
+They entered via TikTok recommendations, took a "try it" posture, and followed: remote bring-forward → dialogue → **spirit (ghost)** regulation → reported improvement.</v>
       </c>
       <c r="E14" t="str" xml:space="preserve">
         <v xml:space="preserve">接受鬼魂控制者绝大多数为耐药性、难治案例。
@@ -1056,7 +1056,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D29" t="str">
-        <v>Among attached spirits, many profiles are especially vivid; a selection follows:</v>
+        <v>Among attached **spirits (ghosts)**, many profiles are especially vivid; a selection follows:</v>
       </c>
       <c r="E29" t="str">
         <v>在众多附体鬼魂中，有多例丰富有趣的案例；此处择要陈列：</v>
@@ -1125,7 +1125,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D32" t="str">
-        <v>July 25 livestream: two attached spirits ghosts on the host jen used a spell to summon the master spirit. For the arrival of the master spirit, one attached spirit ghost feels the guiding spirit with light and love, and the other attached spirit ghost feels the dark knight</v>
+        <v>July 25 livestream: on host Jen, two attached **spirits (ghosts)** used a spell to summon the Master Spirit. For the arrival, one **spirit (ghost)** sensed a guiding presence with light and love; the other **spirit (ghost)** sensed a dark knight.</v>
       </c>
       <c r="E32" t="str">
         <v>七月二十五日直播间，宿主jen身上的两名附体鬼魂在使用咒语召唤高级控制灵后。对于到来的高级控制灵，一名附体鬼魂感受到的是带着光和爱的指导灵，另一名附体鬼魂感受到的是黑暗骑士</v>
@@ -1332,7 +1332,7 @@
         <v>heading</v>
       </c>
       <c r="D41" t="str">
-        <v>Attached spirits (ghosts) brought forward (some hosts: multiple spirits)</v>
+        <v>Attached **spirits** brought forward (some hosts: multiple **spirits**)</v>
       </c>
       <c r="E41" t="str">
         <v>唤出附体鬼魂（部分多灵附体）</v>
@@ -1493,7 +1493,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D48" t="str" xml:space="preserve">
-        <v xml:space="preserve">Within 30 minutes, &gt;80% of human hosts and attached spirits (ghosts) reported marked relief of acute mental distress (spirits in this cohort often showed mental-disorder–like states).
+        <v xml:space="preserve">Within 30 minutes, &gt;80% of human hosts and attached **spirits (ghosts)** reported marked relief of acute mental distress (**spirits (ghosts)** in this cohort often showed mental-disorder–like states).
 Through 24 December 2025, most who improved did not request a second round of regulation — i.e. no relapse in that window by self-report.</v>
       </c>
       <c r="E48" t="str" xml:space="preserve">
@@ -1541,7 +1541,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D50" t="str">
-        <v>From February through December 2025, **Caros Woo** conducted 255+ documented public-service livestreams on TikTok, totaling more than 800 hours. TikTok brought 70,000+ related listeners to the room; there were 1,200+ in-depth interviews; 400+ long-hidden attached spirits were brought forward for dialogue; and 240+ patients with mental-health presentations gained rapid on-stream relief from spirit-related distress.</v>
+        <v>From February through December 2025, **Caros Woo** conducted 255+ documented public-service livestreams on TikTok, totaling more than 800 hours. TikTok brought 70,000+ related listeners to the room; there were 1,200+ in-depth interviews; 400+ long-hidden attached **spirits (ghosts)** were brought forward for dialogue; and 240+ patients with mental-health presentations gained rapid on-stream relief from **spirit (soul)**-related distress.</v>
       </c>
       <c r="E50" t="str">
         <v>在2025年2月至12月，**Caros Woo** 在 TikTok 上进行了 255+ 有记录的公益直播，总时长超过 800 小时。TikTok 推送 70,000+ 高相关人士来访直播间，与 1,200+ 人次深度访谈；其中召唤 400+ 隐藏在患者体内多年的附体鬼魂并与他们深度交流，帮助 240+ 精神障碍患者现场快速改善附体鬼魂带来的痛苦。</v>
@@ -1635,7 +1635,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D54" t="str">
-        <v>TikTok surfaced the following categories of patients in the livestream; attached spirits on each were brought under effective regulation.</v>
+        <v>TikTok surfaced the following categories of patients in the livestream; attached **spirits (ghosts)** on each were brought under effective regulation.</v>
       </c>
       <c r="E54" t="str">
         <v>TikTok 系统推送了以下类别的精神患者来到直播间，他们身上的鬼魂都得到了有效的控制。</v>
@@ -1819,7 +1819,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D62" t="str">
-        <v>(1) A quasi-DID patient with more than 30 identities ---tiktok user name annabella: A large number of attached spirits ghosts in the same host control each other, make trouble with each other and jointly influence the host. The situation is very complicated</v>
+        <v>(1) A quasi-DID patient with more than 30 identities — TikTok username annabella: a large number of attached **spirits (ghosts)** in the same host control each other, make trouble with each other, and jointly influence the host. The situation is very complicated.</v>
       </c>
       <c r="E62" t="str">
         <v>1、身上超过30个身份的DID准患者---tiktok用户名 annabella：同一宿主内大量附体鬼魂之间的相互控制，相互捣乱，共同影响宿主,情况非常复杂</v>
@@ -1842,7 +1842,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D63" t="str">
-        <v>(2)The survivor who escaped from the cult, tiktok user name gabby--- attached spirit ghost, fully reveals how cults and mediums control people at the spiritual level and affect people's health</v>
+        <v>(2) The survivor who escaped from the cult, TikTok username gabby — attached **spirit (ghost)**, fully reveals how cults and mediums control people at the spiritual level and affect people’s health.</v>
       </c>
       <c r="E63" t="str">
         <v>2、从邪教中逃离的幸存者，tiktok用户名 gabby---附体鬼魂完整揭示了邪教，灵媒是如何在灵魂层面控制人，影响人的健康</v>
@@ -1865,7 +1865,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D64" t="str">
-        <v>(3) Tiktok, a delusional patient disguised as a devil and a god, user name idk：--- After playing cards, attached spirits ghosts admit that the sacred identities in paranoia are disguised by themselves and do not exist</v>
+        <v>(3) TikTok, a delusional patient disguised as a devil and a god, username idk — after playing cards, attached **spirits (ghosts)** admit that the sacred identities in paranoia are disguised by themselves and do not exist.</v>
       </c>
       <c r="E64" t="str">
         <v>3、伪装成魔鬼，神明的妄想症患者tiktok用户名 idk：---通过扑克牌实验后，附体鬼魂承认那些妄想症中神圣的身份都是自己伪装的，并不存在</v>
@@ -1888,7 +1888,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D65" t="str">
-        <v>(4) DID gay tiktok user name dominick: attached spirit ghost explained how to turn the host into a homosexual through years of hard work.</v>
+        <v>(4) DID, gay, TikTok username dominick: attached **spirit (ghost)** explained how to turn the host into a homosexual through years of hard work.</v>
       </c>
       <c r="E65" t="str">
         <v>4、DID同性恋tiktok用户名 dominick：：附体鬼魂阐述了是如何通过多年努力将宿主变为一名同性恋</v>
@@ -1980,7 +1980,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D69" t="str">
-        <v>(4) The vast majority of attached spirits are moved into or out of hosts with Master Spirit coordination.</v>
+        <v>(4) The vast majority of attached **spirits (ghosts)** are moved into or out of hosts with Master Spirit coordination.</v>
       </c>
       <c r="E69" t="str">
         <v>4　绝大部分附体鬼魂由高级控制灵协助完成附体或离体。</v>
@@ -2003,7 +2003,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D70" t="str">
-        <v>(5) 100% of American spirits (ghosts) and their hosts are constrained by two prohibitions in UMMA’s soul-control system, so neither side may communicate the true physiology and living conditions of spirits.</v>
+        <v>(5) 100% of American **spirits (ghosts)** and their hosts are constrained by two prohibitions in UMMA’s **spirit (soul)**-control system, so neither side may communicate the true physiology and living conditions of **spirits (ghosts)**.</v>
       </c>
       <c r="E70" t="str">
         <v>5　100% 的美国鬼魂与宿主受 UMMA 灵魂控制系统中两道禁令约束，禁止双方交流鬼魂的真实生理与生存状况。</v>

--- a/docs/page-copy/07-我们的成就.xlsx
+++ b/docs/page-copy/07-我们的成就.xlsx
@@ -710,7 +710,7 @@
       </c>
       <c r="D14" t="str" xml:space="preserve">
         <v xml:space="preserve">Nearly all participants were treatment-resistant, refractory cases.
-They entered via TikTok recommendations, took a "try it" posture, and followed: remote bring-forward → dialogue → **spirit (ghost)** regulation → reported improvement.</v>
+They entered via TikTok recommendations, took a "try it" posture, and followed: remote bring-forward → dialogue → **spirit (ghost)** management → reported improvement.</v>
       </c>
       <c r="E14" t="str" xml:space="preserve">
         <v xml:space="preserve">接受鬼魂控制者绝大多数为耐药性、难治案例。
@@ -803,7 +803,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D18" t="str">
-        <v>Attached spirit (ghost) somatic relocation vs. host symptom improvement — mapping.</v>
+        <v>Attached spirit (ghost) body relocation &amp; movement → host symptom improvement</v>
       </c>
       <c r="E18" t="str">
         <v>附体鬼魂躯体移动，宿主症状改善</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D48" t="str" xml:space="preserve">
         <v xml:space="preserve">Within 30 minutes, &gt;80% of human hosts and attached **spirits (ghosts)** reported marked relief of acute mental distress (**spirits (ghosts)** in this cohort often showed mental-disorder–like states).
-Through 24 December 2025, most who improved did not request a second round of regulation — i.e. no relapse in that window by self-report.</v>
+Till 24 December 2025, most who improved did not request a second round of management &amp; control — i.e. no relapse in that window by self-report.</v>
       </c>
       <c r="E48" t="str" xml:space="preserve">
         <v xml:space="preserve">30 分钟内，&gt;80% 的人类宿主与附体鬼魂双方自觉各类精神痛苦显著缓解（鬼魂侧亦常伴精神障碍样表现）。
@@ -1541,7 +1541,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D50" t="str">
-        <v>From February through December 2025, **Caros Woo** conducted 255+ documented public-service livestreams on TikTok, totaling more than 800 hours. TikTok brought 70,000+ related listeners to the room; there were 1,200+ in-depth interviews; 400+ long-hidden attached **spirits (ghosts)** were brought forward for dialogue; and 240+ patients with mental-health presentations gained rapid on-stream relief from **spirit (soul)**-related distress.</v>
+        <v>From February through December 2025, **Caros Woo** conducted 255+ documented public-service livestreams on TikTok, totaling more than 800 hours. TikTok brought 70,000+ related listeners to the room; there were 1,200+ in-depth interviews; 400+ long-hidden attached **spirits (ghosts)** were brought forward for dialogue; and 240+ patients with mental-health presentations gained rapid on-stream relief from **spirit (ghost)**-related distress.</v>
       </c>
       <c r="E50" t="str">
         <v>在2025年2月至12月，**Caros Woo** 在 TikTok 上进行了 255+ 有记录的公益直播，总时长超过 800 小时。TikTok 推送 70,000+ 高相关人士来访直播间，与 1,200+ 人次深度访谈；其中召唤 400+ 隐藏在患者体内多年的附体鬼魂并与他们深度交流，帮助 240+ 精神障碍患者现场快速改善附体鬼魂带来的痛苦。</v>
@@ -1612,7 +1612,7 @@
         <v>heading</v>
       </c>
       <c r="D53" t="str">
-        <v>I. Data overview</v>
+        <v>Data overview</v>
       </c>
       <c r="E53" t="str">
         <v>第一板块：数据概览</v>
@@ -1635,7 +1635,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D54" t="str">
-        <v>TikTok surfaced the following categories of patients in the livestream; attached **spirits (ghosts)** on each were brought under effective regulation.</v>
+        <v>TikTok surfaced the following categories of patients in the livestream; attached **spirits (ghosts)** on each were brought under effective control.</v>
       </c>
       <c r="E54" t="str">
         <v>TikTok 系统推送了以下类别的精神患者来到直播间，他们身上的鬼魂都得到了有效的控制。</v>
@@ -1658,7 +1658,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D55" t="str">
-        <v>Conditions represented among patients who received contact and effective spirit (ghost) regulation include: schizophrenia, bipolar disorder, depression, anxiety, DID, PTSD, schizoaffective disorder, ADHD, OCD, social phobia, and driving phobia.</v>
+        <v>Conditions represented among patients who received contact and effective spirit (ghost) management include: schizophrenia, bipolar disorder, depression, anxiety, DID, PTSD, schizoaffective disorder, ADHD, OCD, social phobia, and driving phobia.</v>
       </c>
       <c r="E55" t="str">
         <v>病种包括：精分、双向、抑郁、焦虑、多重人格障碍、创伤后遗症、分裂性情感障碍、注意力缺陷综合征、强迫症、社交恐惧症、驾驶恐惧症。</v>
@@ -1750,7 +1750,7 @@
         <v>heading</v>
       </c>
       <c r="D59" t="str">
-        <v>II. Ordinary attached spirit (ghost) management on mental-disorder  pateints</v>
+        <v>Ordinary attached spirit (ghost) management on mental-disorder  pateints</v>
       </c>
       <c r="E59" t="str">
         <v>第二板块：常规精神障碍患者身上的附体鬼魂控制</v>
@@ -1796,7 +1796,7 @@
         <v>heading</v>
       </c>
       <c r="D61" t="str">
-        <v>III. Special illustrative spirit (ghost) regulation cases</v>
+        <v>Special illustrative spirit (ghost) regulation cases</v>
       </c>
       <c r="E61" t="str">
         <v>第三板块：特殊意义鬼魂控制案例展示</v>
@@ -2003,7 +2003,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D70" t="str">
-        <v>(5) 100% of American **spirits (ghosts)** and their hosts are constrained by two prohibitions in UMMA’s **spirit (soul)**-control system, so neither side may communicate the true physiology and living conditions of **spirits (ghosts)**.</v>
+        <v>(5) 100% of American **spirits (ghosts)** and their hosts are constrained by two prohibitions in UMMA’s **spirit **-control system, so neither side may communicate the true physiology and living conditions of **spirits (ghosts)**.</v>
       </c>
       <c r="E70" t="str">
         <v>5　100% 的美国鬼魂与宿主受 UMMA 灵魂控制系统中两道禁令约束，禁止双方交流鬼魂的真实生理与生存状况。</v>
@@ -2187,7 +2187,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D78" t="str">
-        <v>I. Data overview</v>
+        <v>Data overview</v>
       </c>
       <c r="E78" t="str">
         <v>第一板块：数据概览</v>
@@ -2210,7 +2210,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D79" t="str">
-        <v>II. Ordinary attached spirit (ghost) management on mental-disorder  pateints</v>
+        <v>Ordinary attached spirit (ghost) management on mental-disorder  pateints</v>
       </c>
       <c r="E79" t="str">
         <v>第二板块：常规精神障碍患者身上的附体鬼魂控制</v>
@@ -2233,7 +2233,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D80" t="str">
-        <v>III. Special illustrative cases — livestream links</v>
+        <v xml:space="preserve">Special illustrative cases </v>
       </c>
       <c r="E80" t="str">
         <v>第三板块：特殊意义鬼魂控制案例展示</v>
